--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -791,222 +791,347 @@
         <t>Percentage change in reported lease liability.</t>
       </text>
     </comment>
-    <comment ref="B62" authorId="0" shapeId="0">
+    <comment ref="C62" authorId="0" shapeId="0">
+      <text>
+        <t>Current ROU assets − prior ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="D62" authorId="0" shapeId="0">
+      <text>
+        <t>Current ROU assets − prior ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0" shapeId="0">
+      <text>
+        <t>Current ROU assets − prior ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="C63" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="D63" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="E63" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="C64" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="D64" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="E64" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending ROU assets.</t>
+      </text>
+    </comment>
+    <comment ref="C65" authorId="0" shapeId="0">
+      <text>
+        <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+      </text>
+    </comment>
+    <comment ref="D65" authorId="0" shapeId="0">
+      <text>
+        <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0">
+      <text>
+        <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+      </text>
+    </comment>
+    <comment ref="C70" authorId="0" shapeId="0">
+      <text>
+        <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0">
+      <text>
+        <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="0" shapeId="0">
+      <text>
+        <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+      </text>
+    </comment>
+    <comment ref="C71" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTA − prior DTA.</t>
+      </text>
+    </comment>
+    <comment ref="D71" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTA − prior DTA.</t>
+      </text>
+    </comment>
+    <comment ref="E71" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTA − prior DTA.</t>
+      </text>
+    </comment>
+    <comment ref="C72" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTL − prior DTL.</t>
+      </text>
+    </comment>
+    <comment ref="D72" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTL − prior DTL.</t>
+      </text>
+    </comment>
+    <comment ref="E72" authorId="0" shapeId="0">
+      <text>
+        <t>Current DTL − prior DTL.</t>
+      </text>
+    </comment>
+    <comment ref="C73" authorId="0" shapeId="0">
+      <text>
+        <t>Current net position − prior net position.</t>
+      </text>
+    </comment>
+    <comment ref="D73" authorId="0" shapeId="0">
+      <text>
+        <t>Current net position − prior net position.</t>
+      </text>
+    </comment>
+    <comment ref="E73" authorId="0" shapeId="0">
+      <text>
+        <t>Current net position − prior net position.</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for property, plant and equipment.</t>
       </text>
     </comment>
-    <comment ref="C62" authorId="0" shapeId="0">
+    <comment ref="C77" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for property, plant and equipment.</t>
       </text>
     </comment>
-    <comment ref="D62" authorId="0" shapeId="0">
+    <comment ref="D77" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for property, plant and equipment.</t>
       </text>
     </comment>
-    <comment ref="E62" authorId="0" shapeId="0">
+    <comment ref="E77" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for property, plant and equipment.</t>
       </text>
     </comment>
-    <comment ref="B63" authorId="0" shapeId="0">
+    <comment ref="B78" authorId="0" shapeId="0">
       <text>
         <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
       </text>
     </comment>
-    <comment ref="C63" authorId="0" shapeId="0">
+    <comment ref="C78" authorId="0" shapeId="0">
       <text>
         <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
       </text>
     </comment>
-    <comment ref="D63" authorId="0" shapeId="0">
+    <comment ref="D78" authorId="0" shapeId="0">
       <text>
         <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
       </text>
     </comment>
-    <comment ref="E63" authorId="0" shapeId="0">
+    <comment ref="E78" authorId="0" shapeId="0">
       <text>
         <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
       </text>
     </comment>
-    <comment ref="C67" authorId="0" shapeId="0">
+    <comment ref="C82" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D67" authorId="0" shapeId="0">
+    <comment ref="D82" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E67" authorId="0" shapeId="0">
+    <comment ref="E82" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C68" authorId="0" shapeId="0">
+    <comment ref="C83" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D68" authorId="0" shapeId="0">
+    <comment ref="D83" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E68" authorId="0" shapeId="0">
+    <comment ref="E83" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C69" authorId="0" shapeId="0">
+    <comment ref="C84" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D69" authorId="0" shapeId="0">
+    <comment ref="D84" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E69" authorId="0" shapeId="0">
+    <comment ref="E84" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C70" authorId="0" shapeId="0">
+    <comment ref="C85" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D70" authorId="0" shapeId="0">
+    <comment ref="D85" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E70" authorId="0" shapeId="0">
+    <comment ref="E85" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C72" authorId="0" shapeId="0">
+    <comment ref="C87" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D72" authorId="0" shapeId="0">
+    <comment ref="D87" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E72" authorId="0" shapeId="0">
+    <comment ref="E87" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C73" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D73" authorId="0" shapeId="0">
+    <comment ref="D88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E73" authorId="0" shapeId="0">
+    <comment ref="E88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C74" authorId="0" shapeId="0">
+    <comment ref="C89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D74" authorId="0" shapeId="0">
+    <comment ref="D89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E74" authorId="0" shapeId="0">
+    <comment ref="E89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C75" authorId="0" shapeId="0">
+    <comment ref="C90" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D75" authorId="0" shapeId="0">
+    <comment ref="D90" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E75" authorId="0" shapeId="0">
+    <comment ref="E90" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0">
+    <comment ref="C92" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D77" authorId="0" shapeId="0">
+    <comment ref="D92" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E77" authorId="0" shapeId="0">
+    <comment ref="E92" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C78" authorId="0" shapeId="0">
+    <comment ref="C93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D78" authorId="0" shapeId="0">
+    <comment ref="D93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E78" authorId="0" shapeId="0">
+    <comment ref="E93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C79" authorId="0" shapeId="0">
+    <comment ref="C94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0">
+    <comment ref="D94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E79" authorId="0" shapeId="0">
+    <comment ref="E94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C80" authorId="0" shapeId="0">
+    <comment ref="C95" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D80" authorId="0" shapeId="0">
+    <comment ref="D95" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E80" authorId="0" shapeId="0">
+    <comment ref="E95" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -1769,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3648,7 +3773,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C67:E67</t>
+          <t>C82:E82</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -3678,7 +3803,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C68:E68</t>
+          <t>C83:E83</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3708,7 +3833,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C69:E69</t>
+          <t>C84:E84</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -3738,7 +3863,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C70:E70</t>
+          <t>C85:E85</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -3768,7 +3893,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C72:E72</t>
+          <t>C87:E87</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -3798,7 +3923,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C73:E73</t>
+          <t>C88:E88</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -3828,7 +3953,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C74:E74</t>
+          <t>C89:E89</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -3858,7 +3983,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C75:E75</t>
+          <t>C90:E90</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -3888,7 +4013,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C77:E77</t>
+          <t>C92:E92</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -3918,7 +4043,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C78:E78</t>
+          <t>C93:E93</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -3948,7 +4073,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C79:E79</t>
+          <t>C94:E94</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -3978,7 +4103,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C80:E80</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3989,16 +4114,16 @@
     </row>
     <row r="77">
       <c r="A77" s="10" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Change in Right-of-use Assets</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2024–2026 (3 cells)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -4008,7 +4133,7 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>B62:E62</t>
+          <t>C62:E62</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -4019,29 +4144,269 @@
     </row>
     <row r="78">
       <c r="A78" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Right-of-use Assets Growth</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>C63:E63</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>rou_assets_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>C64:E64</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>C65:E65</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>average_rou_assets, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>B70:E70</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>C71:E71</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>C72:E72</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>C73:E73</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>B77:E77</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>PP&amp;E Capex / Revenue</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>2023–2026 (4 cells)</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>B63:E63</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>B78:E78</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, revenue_link</t>
         </is>
@@ -4501,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S249"/>
+  <dimension ref="A1:S274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20781,11 +21146,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C82</t>
         </is>
       </c>
       <c r="I206">
-        <f>C66-B66</f>
+        <f>C81-B81</f>
         <v/>
       </c>
       <c r="J206" t="n">
@@ -20857,11 +21222,11 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D67</t>
+          <t>D82</t>
         </is>
       </c>
       <c r="I207">
-        <f>D66-C66</f>
+        <f>D81-C81</f>
         <v/>
       </c>
       <c r="J207" t="n">
@@ -20933,11 +21298,11 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>E67</t>
+          <t>E82</t>
         </is>
       </c>
       <c r="I208">
-        <f>E66-D66</f>
+        <f>E81-D81</f>
         <v/>
       </c>
       <c r="J208" t="n">
@@ -21009,11 +21374,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C83</t>
         </is>
       </c>
       <c r="I209">
-        <f>IF(B66=0,NA(),C66/B66-1)</f>
+        <f>IF(B81=0,NA(),C81/B81-1)</f>
         <v/>
       </c>
       <c r="J209" t="n">
@@ -21090,11 +21455,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>D68</t>
+          <t>D83</t>
         </is>
       </c>
       <c r="I210">
-        <f>IF(C66=0,NA(),D66/C66-1)</f>
+        <f>IF(C81=0,NA(),D81/C81-1)</f>
         <v/>
       </c>
       <c r="J210" t="n">
@@ -21171,11 +21536,11 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>E68</t>
+          <t>E83</t>
         </is>
       </c>
       <c r="I211">
-        <f>IF(D66=0,NA(),E66/D66-1)</f>
+        <f>IF(D81=0,NA(),E81/D81-1)</f>
         <v/>
       </c>
       <c r="J211" t="n">
@@ -21252,11 +21617,11 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="I212">
-        <f>(B66+C66)/2</f>
+        <f>(B81+C81)/2</f>
         <v/>
       </c>
       <c r="J212" t="n">
@@ -21328,11 +21693,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>D69</t>
+          <t>D84</t>
         </is>
       </c>
       <c r="I213">
-        <f>(C66+D66)/2</f>
+        <f>(C81+D81)/2</f>
         <v/>
       </c>
       <c r="J213" t="n">
@@ -21404,11 +21769,11 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>E69</t>
+          <t>E84</t>
         </is>
       </c>
       <c r="I214">
-        <f>(D66+E66)/2</f>
+        <f>(D81+E81)/2</f>
         <v/>
       </c>
       <c r="J214" t="n">
@@ -21480,11 +21845,11 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C85</t>
         </is>
       </c>
       <c r="I215">
-        <f>IF('Condensed Financials'!C34=0,NA(),C69/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C84/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J215" t="n">
@@ -21561,11 +21926,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>D70</t>
+          <t>D85</t>
         </is>
       </c>
       <c r="I216">
-        <f>IF('Condensed Financials'!D34=0,NA(),D69/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D84/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J216" t="n">
@@ -21642,11 +22007,11 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>E70</t>
+          <t>E85</t>
         </is>
       </c>
       <c r="I217">
-        <f>IF('Condensed Financials'!E34=0,NA(),E69/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E84/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J217" t="n">
@@ -21723,11 +22088,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C87</t>
         </is>
       </c>
       <c r="I218">
-        <f>C71-B71</f>
+        <f>C86-B86</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -21799,11 +22164,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D72</t>
+          <t>D87</t>
         </is>
       </c>
       <c r="I219">
-        <f>D71-C71</f>
+        <f>D86-C86</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -21875,11 +22240,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E72</t>
+          <t>E87</t>
         </is>
       </c>
       <c r="I220">
-        <f>E71-D71</f>
+        <f>E86-D86</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -21951,11 +22316,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C73</t>
+          <t>C88</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B71=0,NA(),C71/B71-1)</f>
+        <f>IF(B86=0,NA(),C86/B86-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -22032,11 +22397,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D73</t>
+          <t>D88</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C71=0,NA(),D71/C71-1)</f>
+        <f>IF(C86=0,NA(),D86/C86-1)</f>
         <v/>
       </c>
       <c r="J222" t="e">
@@ -22113,11 +22478,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E73</t>
+          <t>E88</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D71=0,NA(),E71/D71-1)</f>
+        <f>IF(D86=0,NA(),E86/D86-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -22194,11 +22559,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C74</t>
+          <t>C89</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B71+C71)/2</f>
+        <f>(B86+C86)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -22270,11 +22635,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D74</t>
+          <t>D89</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C71+D71)/2</f>
+        <f>(C86+D86)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -22346,11 +22711,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E74</t>
+          <t>E89</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D71+E71)/2</f>
+        <f>(D86+E86)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -22422,11 +22787,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C75</t>
+          <t>C90</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C74/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -22503,11 +22868,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D75</t>
+          <t>D90</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D74/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -22584,11 +22949,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E75</t>
+          <t>E90</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E74/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -22665,11 +23030,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C77</t>
+          <t>C92</t>
         </is>
       </c>
       <c r="I230">
-        <f>C76-B76</f>
+        <f>C91-B91</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -22741,11 +23106,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D77</t>
+          <t>D92</t>
         </is>
       </c>
       <c r="I231">
-        <f>D76-C76</f>
+        <f>D91-C91</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -22817,11 +23182,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E77</t>
+          <t>E92</t>
         </is>
       </c>
       <c r="I232">
-        <f>E76-D76</f>
+        <f>E91-D91</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -22893,11 +23258,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C78</t>
+          <t>C93</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B76=0,NA(),C76/B76-1)</f>
+        <f>IF(B91=0,NA(),C91/B91-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -22974,11 +23339,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D78</t>
+          <t>D93</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C76=0,NA(),D76/C76-1)</f>
+        <f>IF(C91=0,NA(),D91/C91-1)</f>
         <v/>
       </c>
       <c r="J234" t="n">
@@ -23055,11 +23420,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E78</t>
+          <t>E93</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D76=0,NA(),E76/D76-1)</f>
+        <f>IF(D91=0,NA(),E91/D91-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -23136,11 +23501,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C79</t>
+          <t>C94</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B76+C76)/2</f>
+        <f>(B91+C91)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -23212,11 +23577,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D79</t>
+          <t>D94</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C76+D76)/2</f>
+        <f>(C91+D91)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -23288,11 +23653,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E79</t>
+          <t>E94</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D76+E76)/2</f>
+        <f>(D91+E91)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -23364,11 +23729,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C80</t>
+          <t>C95</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C79/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -23445,11 +23810,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D80</t>
+          <t>D95</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D79/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -23526,11 +23891,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E80</t>
+          <t>E95</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E79/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -23574,7 +23939,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ppe_capex__20230129</t>
+          <t>rou_assets_change__20240128</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -23582,22 +23947,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Change in Right-of-use Assets</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Presented as −reported payments for property, plant and equipment.</t>
+          <t>Current ROU assets − prior ROU assets.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>capex.ppe_capex.2023-01-29</t>
+          <t>lease_rou.rou_assets_change.2024-01-28</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -23607,22 +23972,22 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>B62</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="I242">
-        <f>-B61</f>
+        <f>C61-B61</f>
         <v/>
       </c>
       <c r="J242" t="n">
-        <v>638657</v>
+        <v>296191</v>
       </c>
       <c r="K242" t="n">
         <v>0.01</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+          <t>Change in Right-of-use Assets = Current − Prior reported ROU assets.|Balance change is not lease cash payments, amortization, or liability change.</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -23632,25 +23997,25 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>ppe_capex</t>
+          <t>rou_assets_change</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2024-01-28</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ppe_capex__20240128</t>
+          <t>rou_assets_change__20250202</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -23658,22 +24023,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Change in Right-of-use Assets</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Presented as −reported payments for property, plant and equipment.</t>
+          <t>Current ROU assets − prior ROU assets.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>capex.ppe_capex.2024-01-28</t>
+          <t>lease_rou.rou_assets_change.2025-02-02</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -23683,22 +24048,22 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>D62</t>
         </is>
       </c>
       <c r="I243">
-        <f>-C61</f>
+        <f>D61-C61</f>
         <v/>
       </c>
       <c r="J243" t="n">
-        <v>651865</v>
+        <v>150646</v>
       </c>
       <c r="K243" t="n">
         <v>0.01</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+          <t>Change in Right-of-use Assets = Current − Prior reported ROU assets.|Balance change is not lease cash payments, amortization, or liability change.</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -23708,25 +24073,25 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>ppe_capex</t>
+          <t>rou_assets_change</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="R243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2025-02-02</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ppe_capex__20250202</t>
+          <t>rou_assets_change__20260201</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -23734,22 +24099,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Change in Right-of-use Assets</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Presented as −reported payments for property, plant and equipment.</t>
+          <t>Current ROU assets − prior ROU assets.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>capex.ppe_capex.2025-02-02</t>
+          <t>lease_rou.rou_assets_change.2026-02-01</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -23759,22 +24124,22 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>D62</t>
+          <t>E62</t>
         </is>
       </c>
       <c r="I244">
-        <f>-D61</f>
+        <f>E61-D61</f>
         <v/>
       </c>
       <c r="J244" t="n">
-        <v>689232</v>
+        <v>213925</v>
       </c>
       <c r="K244" t="n">
         <v>0.01</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+          <t>Change in Right-of-use Assets = Current − Prior reported ROU assets.|Balance change is not lease cash payments, amortization, or liability change.</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -23784,25 +24149,25 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>ppe_capex</t>
+          <t>rou_assets_change</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="R244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2026-02-01</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ppe_capex__20260201</t>
+          <t>rou_assets_growth__20240128</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -23810,22 +24175,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Right-of-use Assets Growth</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Presented as −reported payments for property, plant and equipment.</t>
+          <t>Percentage change in reported ROU assets.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>capex.ppe_capex.2026-02-01</t>
+          <t>lease_rou.rou_assets_growth.2024-01-28</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -23835,22 +24200,27 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>E62</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="I245">
-        <f>-E61</f>
+        <f>IF(B61=0,NA(),C61/B61-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
-        <v>680802</v>
+        <v>0.3055345521389616</v>
       </c>
       <c r="K245" t="n">
         <v>0.01</v>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>rou_assets_change__20240128</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+          <t>Right-of-use Assets Growth = Change in ROU assets / Prior ROU assets.|A zero prior ROU-asset balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, or liability growth.</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -23860,25 +24230,25 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>ppe_capex</t>
+          <t>rou_assets_growth</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="R245" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-01-28</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue__20230129</t>
+          <t>rou_assets_growth__20250202</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -23886,22 +24256,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
+          <t>Right-of-use Assets Growth</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+          <t>Percentage change in reported ROU assets.</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>capex.ppe_capex_to_revenue.2023-01-29</t>
+          <t>lease_rou.rou_assets_growth.2025-02-02</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -23911,27 +24281,27 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>B63</t>
+          <t>D63</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF('Condensed Financials'!B34=0,NA(),B62/'Condensed Financials'!B34)</f>
+        <f>IF(C61=0,NA(),D61/C61-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
-        <v>0.07874429228811279</v>
+        <v>0.1190303490016672</v>
       </c>
       <c r="K246" t="n">
         <v>0.01</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>ppe_capex__20230129,revenue_link__20230129</t>
+          <t>rou_assets_change__20250202</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+          <t>Right-of-use Assets Growth = Change in ROU assets / Prior ROU assets.|A zero prior ROU-asset balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, or liability growth.</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -23941,25 +24311,25 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue</t>
+          <t>rou_assets_growth</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue__20240128</t>
+          <t>rou_assets_growth__20260201</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -23967,22 +24337,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
+          <t>Right-of-use Assets Growth</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+          <t>Percentage change in reported ROU assets.</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>capex.ppe_capex_to_revenue.2024-01-28</t>
+          <t>lease_rou.rou_assets_growth.2026-02-01</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -23992,27 +24362,27 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>E63</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF('Condensed Financials'!C34=0,NA(),C62/'Condensed Financials'!C34)</f>
+        <f>IF(D61=0,NA(),E61/D61-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
-        <v>0.06776652052264213</v>
+        <v>0.1510496689863979</v>
       </c>
       <c r="K247" t="n">
         <v>0.01</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>ppe_capex__20240128,revenue_link__20240128</t>
+          <t>rou_assets_change__20260201</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+          <t>Right-of-use Assets Growth = Change in ROU assets / Prior ROU assets.|A zero prior ROU-asset balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, or liability growth.</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -24022,25 +24392,25 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue</t>
+          <t>rou_assets_growth</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="R247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue__20250202</t>
+          <t>average_rou_assets__20240128</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -24048,22 +24418,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
+          <t>Average Right-of-use Assets</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+          <t>Average beginning and ending ROU assets.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>capex.ppe_capex_to_revenue.2025-02-02</t>
+          <t>lease_rou.average_rou_assets.2024-01-28</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -24073,27 +24443,22 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>D63</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="I248">
-        <f>IF('Condensed Financials'!D34=0,NA(),D62/'Condensed Financials'!D34)</f>
+        <f>(B61+C61)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
-        <v>0.0650948052563787</v>
+        <v>1117514.5</v>
       </c>
       <c r="K248" t="n">
         <v>0.01</v>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>ppe_capex__20250202,revenue_link__20250202</t>
-        </is>
-      </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+          <t>Average Right-of-use Assets = (Prior ROU assets + Current ROU assets) / 2.</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -24103,25 +24468,25 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue</t>
+          <t>average_rou_assets</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="R248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2024-01-28</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ppe_capex_to_revenue__20260201</t>
+          <t>average_rou_assets__20250202</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -24129,22 +24494,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
+          <t>Average Right-of-use Assets</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+          <t>Average beginning and ending ROU assets.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>capex.ppe_capex_to_revenue.2026-02-01</t>
+          <t>lease_rou.average_rou_assets.2025-02-02</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lease_rou</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -24154,46 +24519,1991 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>E63</t>
+          <t>D64</t>
         </is>
       </c>
       <c r="I249">
-        <f>IF('Condensed Financials'!E34=0,NA(),E62/'Condensed Financials'!E34)</f>
+        <f>(C61+D61)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
-        <v>0.06131915046925945</v>
+        <v>1340933</v>
       </c>
       <c r="K249" t="n">
         <v>0.01</v>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets = (Prior ROU assets + Current ROU assets) / 2.</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>average_rou_assets</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>114</v>
+      </c>
+      <c r="R249" t="n">
+        <v>2</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>average_rou_assets__20260201</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>249</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Average beginning and ending ROU assets.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>lease_rou.average_rou_assets.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>lease_rou</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>E64</t>
+        </is>
+      </c>
+      <c r="I250">
+        <f>(D61+E61)/2</f>
+        <v/>
+      </c>
+      <c r="J250" t="n">
+        <v>1523218.5</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets = (Prior ROU assets + Current ROU assets) / 2.</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>average_rou_assets</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>114</v>
+      </c>
+      <c r="R250" t="n">
+        <v>3</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue__20240128</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>250</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>lease_rou.rou_assets_to_revenue.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>lease_rou</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>C65</t>
+        </is>
+      </c>
+      <c r="I251">
+        <f>IF('Condensed Financials'!C34=0,NA(),C64/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="J251" t="n">
+        <v>0.1161744675639897</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>average_rou_assets__20240128,revenue_link__20240128</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue uses the average balance, not the ending level alone.|Intensity is balance context only — not lease payments, discount rates, amortization, or liability reconciliation.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>115</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue__20250202</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>251</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>lease_rou.rou_assets_to_revenue.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>lease_rou</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="I252">
+        <f>IF('Condensed Financials'!D34=0,NA(),D64/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="J252" t="n">
+        <v>0.1266449794798437</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>average_rou_assets__20250202,revenue_link__20250202</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue uses the average balance, not the ending level alone.|Intensity is balance context only — not lease payments, discount rates, amortization, or liability reconciliation.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>115</v>
+      </c>
+      <c r="R252" t="n">
+        <v>2</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue__20260201</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>252</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Average ROU assets divided by current Revenue (balance intensity).</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>lease_rou.rou_assets_to_revenue.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>lease_rou</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>E65</t>
+        </is>
+      </c>
+      <c r="I253">
+        <f>IF('Condensed Financials'!E34=0,NA(),E64/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+      <c r="J253" t="n">
+        <v>0.1371947561832364</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>average_rou_assets__20260201,revenue_link__20260201</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue uses the average balance, not the ending level alone.|Intensity is balance context only — not lease payments, discount rates, amortization, or liability reconciliation.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>rou_assets_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>115</v>
+      </c>
+      <c r="R253" t="n">
+        <v>3</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20230129</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>253</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>B70</t>
+        </is>
+      </c>
+      <c r="I254">
+        <f>B68-B69</f>
+        <v/>
+      </c>
+      <c r="J254" t="n">
+        <v>-48682</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position = Deferred tax assets − Deferred tax liabilities (same period).|Analytical DTA less DTL only — not deferred-tax expense, cash taxes, recoverability, or legal offset eligibility.</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>116</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20240128</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>254</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>C70</t>
+        </is>
+      </c>
+      <c r="I255">
+        <f>C68-C69</f>
+        <v/>
+      </c>
+      <c r="J255" t="n">
+        <v>-20346</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position = Deferred tax assets − Deferred tax liabilities (same period).|Analytical DTA less DTL only — not deferred-tax expense, cash taxes, recoverability, or legal offset eligibility.</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>116</v>
+      </c>
+      <c r="R255" t="n">
+        <v>1</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20250202</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>255</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D70</t>
+        </is>
+      </c>
+      <c r="I256">
+        <f>D68-D69</f>
+        <v/>
+      </c>
+      <c r="J256" t="n">
+        <v>-81103</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position = Deferred tax assets − Deferred tax liabilities (same period).|Analytical DTA less DTL only — not deferred-tax expense, cash taxes, recoverability, or legal offset eligibility.</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>116</v>
+      </c>
+      <c r="R256" t="n">
+        <v>2</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20260201</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>256</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Analytical net position = Deferred tax assets − Deferred tax liabilities.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>E70</t>
+        </is>
+      </c>
+      <c r="I257">
+        <f>E68-E69</f>
+        <v/>
+      </c>
+      <c r="J257" t="n">
+        <v>-28241</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position = Deferred tax assets − Deferred tax liabilities (same period).|Analytical DTA less DTL only — not deferred-tax expense, cash taxes, recoverability, or legal offset eligibility.</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>116</v>
+      </c>
+      <c r="R257" t="n">
+        <v>3</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change__20240128</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>257</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Current DTA − prior DTA.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_assets_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>C71</t>
+        </is>
+      </c>
+      <c r="I258">
+        <f>C68-B68</f>
+        <v/>
+      </c>
+      <c r="J258" t="n">
+        <v>2774</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets = Current DTA − Prior DTA.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>117</v>
+      </c>
+      <c r="R258" t="n">
+        <v>1</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change__20250202</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>258</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Current DTA − prior DTA.</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_assets_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D71</t>
+        </is>
+      </c>
+      <c r="I259">
+        <f>D68-C68</f>
+        <v/>
+      </c>
+      <c r="J259" t="n">
+        <v>7909</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets = Current DTA − Prior DTA.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>117</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change__20260201</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>259</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Current DTA − prior DTA.</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_assets_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>E71</t>
+        </is>
+      </c>
+      <c r="I260">
+        <f>E68-D68</f>
+        <v/>
+      </c>
+      <c r="J260" t="n">
+        <v>6952</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets = Current DTA − Prior DTA.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>deferred_tax_assets_change</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>117</v>
+      </c>
+      <c r="R260" t="n">
+        <v>3</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change__20240128</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>260</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Current DTL − prior DTL.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_liabilities_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>C72</t>
+        </is>
+      </c>
+      <c r="I261">
+        <f>C69-B69</f>
+        <v/>
+      </c>
+      <c r="J261" t="n">
+        <v>-25562</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities = Current DTL − Prior DTL.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>118</v>
+      </c>
+      <c r="R261" t="n">
+        <v>1</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change__20250202</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>261</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Current DTL − prior DTL.</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_liabilities_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+      <c r="I262">
+        <f>D69-C69</f>
+        <v/>
+      </c>
+      <c r="J262" t="n">
+        <v>68666</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities = Current DTL − Prior DTL.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>118</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change__20260201</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>262</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Current DTL − prior DTL.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>deferred_tax.deferred_tax_liabilities_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>E72</t>
+        </is>
+      </c>
+      <c r="I263">
+        <f>E69-D69</f>
+        <v/>
+      </c>
+      <c r="J263" t="n">
+        <v>-45910</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities = Current DTL − Prior DTL.|Balance movement only — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>deferred_tax_liabilities_change</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>118</v>
+      </c>
+      <c r="R263" t="n">
+        <v>3</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change__20240128</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>263</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Current net position − prior net position.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>C73</t>
+        </is>
+      </c>
+      <c r="I264">
+        <f>C70-B70</f>
+        <v/>
+      </c>
+      <c r="J264" t="n">
+        <v>28336</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20240128,net_deferred_tax_position__20230129</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position = Current net − Prior net.|Net-position change is a balance movement — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>119</v>
+      </c>
+      <c r="R264" t="n">
+        <v>1</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change__20250202</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>264</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Current net position − prior net position.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+      <c r="I265">
+        <f>D70-C70</f>
+        <v/>
+      </c>
+      <c r="J265" t="n">
+        <v>-60757</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20250202,net_deferred_tax_position__20240128</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position = Current net − Prior net.|Net-position change is a balance movement — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>119</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change__20260201</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>265</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Current net position − prior net position.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>deferred_tax.net_deferred_tax_position_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>deferred_tax</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>E73</t>
+        </is>
+      </c>
+      <c r="I266">
+        <f>E70-D70</f>
+        <v/>
+      </c>
+      <c r="J266" t="n">
+        <v>52862</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position__20260201,net_deferred_tax_position__20250202</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position = Current net − Prior net.|Net-position change is a balance movement — not deferred-tax expense or cash taxes.</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position_change</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>119</v>
+      </c>
+      <c r="R266" t="n">
+        <v>3</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230129</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>266</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Presented as −reported payments for property, plant and equipment.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>B77</t>
+        </is>
+      </c>
+      <c r="I267">
+        <f>-B76</f>
+        <v/>
+      </c>
+      <c r="J267" t="n">
+        <v>638657</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>120</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240128</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>267</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Presented as −reported payments for property, plant and equipment.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>C77</t>
+        </is>
+      </c>
+      <c r="I268">
+        <f>-C76</f>
+        <v/>
+      </c>
+      <c r="J268" t="n">
+        <v>651865</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>120</v>
+      </c>
+      <c r="R268" t="n">
+        <v>1</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250202</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>268</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Presented as −reported payments for property, plant and equipment.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D77</t>
+        </is>
+      </c>
+      <c r="I269">
+        <f>-D76</f>
+        <v/>
+      </c>
+      <c r="J269" t="n">
+        <v>689232</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>120</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ppe_capex__20260201</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>269</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Presented as −reported payments for property, plant and equipment.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>E77</t>
+        </is>
+      </c>
+      <c r="I270">
+        <f>-E76</f>
+        <v/>
+      </c>
+      <c r="J270" t="n">
+        <v>680802</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex = −(reported payments for property, plant and equipment).|Do not apply absolute value; keep the −reported sign convention consistently.|Explicit zero reported payments remain valid (zero capex).</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>120</v>
+      </c>
+      <c r="R270" t="n">
+        <v>3</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue__20230129</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>270</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex_to_revenue.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>B78</t>
+        </is>
+      </c>
+      <c r="I271">
+        <f>IF('Condensed Financials'!B34=0,NA(),B77/'Condensed Financials'!B34)</f>
+        <v/>
+      </c>
+      <c r="J271" t="n">
+        <v>0.07874429228811279</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230129,revenue_link__20230129</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>121</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue__20240128</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>271</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex_to_revenue.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>C78</t>
+        </is>
+      </c>
+      <c r="I272">
+        <f>IF('Condensed Financials'!C34=0,NA(),C77/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="J272" t="n">
+        <v>0.06776652052264213</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240128,revenue_link__20240128</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>121</v>
+      </c>
+      <c r="R272" t="n">
+        <v>1</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue__20250202</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>272</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex_to_revenue.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="I273">
+        <f>IF('Condensed Financials'!D34=0,NA(),D77/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="J273" t="n">
+        <v>0.0650948052563787</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250202,revenue_link__20250202</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>121</v>
+      </c>
+      <c r="R273" t="n">
+        <v>2</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ppe_capex_to_revenue__20260201</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>273</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>capex.ppe_capex_to_revenue.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>E78</t>
+        </is>
+      </c>
+      <c r="I274">
+        <f>IF('Condensed Financials'!E34=0,NA(),E77/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+      <c r="J274" t="n">
+        <v>0.06131915046925945</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L274" t="inlineStr">
         <is>
           <t>ppe_capex__20260201,revenue_link__20260201</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
+      <c r="M274" t="inlineStr">
         <is>
           <t>PP&amp;E Capex / Revenue uses the −reported payment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity only — not a reinvestment bridge or depreciation ratio.</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr">
+      <c r="O274" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr">
+      <c r="P274" t="inlineStr">
         <is>
           <t>ppe_capex_to_revenue</t>
         </is>
       </c>
-      <c r="Q249" t="n">
+      <c r="Q274" t="n">
         <v>121</v>
       </c>
-      <c r="R249" t="n">
+      <c r="R274" t="n">
         <v>3</v>
       </c>
-      <c r="S249" t="inlineStr">
+      <c r="S274" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -27278,7 +29588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -28444,381 +30754,622 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E CAPEX CONTEXT</t>
+          <t>LEASE ROU-ASSET CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Payments for Property, Plant &amp; Equipment (reported)</t>
+          <t>Right-of-use Assets</t>
         </is>
       </c>
       <c r="B61" s="12">
-        <f>'Cash Flow Statement'!B15</f>
+        <f>'Balance Sheet'!B26</f>
         <v/>
       </c>
       <c r="C61" s="12">
-        <f>'Cash Flow Statement'!C15</f>
+        <f>'Balance Sheet'!C26</f>
         <v/>
       </c>
       <c r="D61" s="12">
-        <f>'Cash Flow Statement'!D15</f>
+        <f>'Balance Sheet'!D26</f>
         <v/>
       </c>
       <c r="E61" s="12">
-        <f>'Cash Flow Statement'!E15</f>
+        <f>'Balance Sheet'!E26</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
-        </is>
-      </c>
-      <c r="B62" s="15">
-        <f>-B61</f>
-        <v/>
+          <t>Change in Right-of-use Assets</t>
+        </is>
       </c>
       <c r="C62" s="15">
-        <f>-C61</f>
+        <f>C61-B61</f>
         <v/>
       </c>
       <c r="D62" s="15">
-        <f>-D61</f>
+        <f>D61-C61</f>
         <v/>
       </c>
       <c r="E62" s="15">
-        <f>-E61</f>
+        <f>E61-D61</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
-        </is>
-      </c>
-      <c r="B63" s="14">
-        <f>IF('Condensed Financials'!B34=0,NA(),B62/'Condensed Financials'!B34)</f>
-        <v/>
+          <t>Right-of-use Assets Growth</t>
+        </is>
       </c>
       <c r="C63" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C62/'Condensed Financials'!C34)</f>
+        <f>IF(B61=0,NA(),C61/B61-1)</f>
         <v/>
       </c>
       <c r="D63" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D62/'Condensed Financials'!D34)</f>
+        <f>IF(C61=0,NA(),D61/C61-1)</f>
         <v/>
       </c>
       <c r="E63" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E62/'Condensed Financials'!E34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64"/>
+        <f>IF(D61=0,NA(),E61/D61-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="C64" s="15">
+        <f>(B61+C61)/2</f>
+        <v/>
+      </c>
+      <c r="D64" s="15">
+        <f>(C61+D61)/2</f>
+        <v/>
+      </c>
+      <c r="E64" s="15">
+        <f>(D61+E61)/2</f>
+        <v/>
+      </c>
+    </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B66" s="12">
-        <f>'Balance Sheet'!B22</f>
-        <v/>
-      </c>
-      <c r="C66" s="12">
-        <f>'Balance Sheet'!C22</f>
-        <v/>
-      </c>
-      <c r="D66" s="12">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
-      </c>
-      <c r="E66" s="12">
-        <f>'Balance Sheet'!E22</f>
-        <v/>
-      </c>
-    </row>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C65" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C64/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D65" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D64/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E65" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E64/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C67" s="15">
-        <f>C66-B66</f>
-        <v/>
-      </c>
-      <c r="D67" s="15">
-        <f>D66-C66</f>
-        <v/>
-      </c>
-      <c r="E67" s="15">
-        <f>E66-D66</f>
-        <v/>
+          <t>DEFERRED-TAX BALANCE CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C68" s="14">
-        <f>IF(B66=0,NA(),C66/B66-1)</f>
-        <v/>
-      </c>
-      <c r="D68" s="14">
-        <f>IF(C66=0,NA(),D66/C66-1)</f>
-        <v/>
-      </c>
-      <c r="E68" s="14">
-        <f>IF(D66=0,NA(),E66/D66-1)</f>
+          <t>Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="12">
+        <f>'Balance Sheet'!B21</f>
+        <v/>
+      </c>
+      <c r="C68" s="12">
+        <f>'Balance Sheet'!C21</f>
+        <v/>
+      </c>
+      <c r="D68" s="12">
+        <f>'Balance Sheet'!D21</f>
+        <v/>
+      </c>
+      <c r="E68" s="12">
+        <f>'Balance Sheet'!E21</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C69" s="15">
-        <f>(B66+C66)/2</f>
-        <v/>
-      </c>
-      <c r="D69" s="15">
-        <f>(C66+D66)/2</f>
-        <v/>
-      </c>
-      <c r="E69" s="15">
-        <f>(D66+E66)/2</f>
+          <t>Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="B69" s="12">
+        <f>'Balance Sheet'!B27</f>
+        <v/>
+      </c>
+      <c r="C69" s="12">
+        <f>'Balance Sheet'!C27</f>
+        <v/>
+      </c>
+      <c r="D69" s="12">
+        <f>'Balance Sheet'!D27</f>
+        <v/>
+      </c>
+      <c r="E69" s="12">
+        <f>'Balance Sheet'!E27</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C70" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C69/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D70" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D69/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E70" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E69/'Condensed Financials'!E34)</f>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="B70" s="15">
+        <f>B68-B69</f>
+        <v/>
+      </c>
+      <c r="C70" s="15">
+        <f>C68-C69</f>
+        <v/>
+      </c>
+      <c r="D70" s="15">
+        <f>D68-D69</f>
+        <v/>
+      </c>
+      <c r="E70" s="15">
+        <f>E68-E69</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B71" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C71" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D71" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E71" s="12">
-        <f>'Balance Sheet'!E23</f>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="C71" s="15">
+        <f>C68-B68</f>
+        <v/>
+      </c>
+      <c r="D71" s="15">
+        <f>D68-C68</f>
+        <v/>
+      </c>
+      <c r="E71" s="15">
+        <f>E68-D68</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Deferred Tax Liabilities</t>
         </is>
       </c>
       <c r="C72" s="15">
-        <f>C71-B71</f>
+        <f>C69-B69</f>
         <v/>
       </c>
       <c r="D72" s="15">
-        <f>D71-C71</f>
+        <f>D69-C69</f>
         <v/>
       </c>
       <c r="E72" s="15">
-        <f>E71-D71</f>
+        <f>E69-D69</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C73" s="14">
-        <f>IF(B71=0,NA(),C71/B71-1)</f>
-        <v/>
-      </c>
-      <c r="D73" s="14">
-        <f>IF(C71=0,NA(),D71/C71-1)</f>
-        <v/>
-      </c>
-      <c r="E73" s="14">
-        <f>IF(D71=0,NA(),E71/D71-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C74" s="15">
-        <f>(B71+C71)/2</f>
-        <v/>
-      </c>
-      <c r="D74" s="15">
-        <f>(C71+D71)/2</f>
-        <v/>
-      </c>
-      <c r="E74" s="15">
-        <f>(D71+E71)/2</f>
-        <v/>
-      </c>
-    </row>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="C73" s="15">
+        <f>C70-B70</f>
+        <v/>
+      </c>
+      <c r="D73" s="15">
+        <f>D70-C70</f>
+        <v/>
+      </c>
+      <c r="E73" s="15">
+        <f>E70-D70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C75" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C74/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D75" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D74/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E75" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E74/'Condensed Financials'!E34)</f>
-        <v/>
+          <t>PP&amp;E CAPEX CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Payments for Property, Plant &amp; Equipment (reported)</t>
         </is>
       </c>
       <c r="B76" s="12">
-        <f>B66+B71</f>
+        <f>'Cash Flow Statement'!B15</f>
         <v/>
       </c>
       <c r="C76" s="12">
-        <f>C66+C71</f>
+        <f>'Cash Flow Statement'!C15</f>
         <v/>
       </c>
       <c r="D76" s="12">
-        <f>D66+D71</f>
+        <f>'Cash Flow Statement'!D15</f>
         <v/>
       </c>
       <c r="E76" s="12">
-        <f>E66+E71</f>
+        <f>'Cash Flow Statement'!E15</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="B77" s="15">
+        <f>-B76</f>
+        <v/>
       </c>
       <c r="C77" s="15">
-        <f>C76-B76</f>
+        <f>-C76</f>
         <v/>
       </c>
       <c r="D77" s="15">
-        <f>D76-C76</f>
+        <f>-D76</f>
         <v/>
       </c>
       <c r="E77" s="15">
-        <f>E76-D76</f>
+        <f>-E76</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="14">
+        <f>IF('Condensed Financials'!B34=0,NA(),B77/'Condensed Financials'!B34)</f>
+        <v/>
       </c>
       <c r="C78" s="14">
-        <f>IF(B76=0,NA(),C76/B76-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C77/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D78" s="14">
-        <f>IF(C76=0,NA(),D76/C76-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D77/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E78" s="14">
-        <f>IF(D76=0,NA(),E76/D76-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C79" s="15">
-        <f>(B76+C76)/2</f>
-        <v/>
-      </c>
-      <c r="D79" s="15">
-        <f>(C76+D76)/2</f>
-        <v/>
-      </c>
-      <c r="E79" s="15">
-        <f>(D76+E76)/2</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF('Condensed Financials'!E34=0,NA(),E77/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B81" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C81" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D81" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E81" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C82" s="15">
+        <f>C81-B81</f>
+        <v/>
+      </c>
+      <c r="D82" s="15">
+        <f>D81-C81</f>
+        <v/>
+      </c>
+      <c r="E82" s="15">
+        <f>E81-D81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C83" s="14">
+        <f>IF(B81=0,NA(),C81/B81-1)</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IF(C81=0,NA(),D81/C81-1)</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IF(D81=0,NA(),E81/D81-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C84" s="15">
+        <f>(B81+C81)/2</f>
+        <v/>
+      </c>
+      <c r="D84" s="15">
+        <f>(C81+D81)/2</f>
+        <v/>
+      </c>
+      <c r="E84" s="15">
+        <f>(D81+E81)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C85" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C84/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D85" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D84/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E84/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B86" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C86" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D86" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E86" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C87" s="15">
+        <f>C86-B86</f>
+        <v/>
+      </c>
+      <c r="D87" s="15">
+        <f>D86-C86</f>
+        <v/>
+      </c>
+      <c r="E87" s="15">
+        <f>E86-D86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C88" s="14">
+        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <v/>
+      </c>
+      <c r="D88" s="14">
+        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>IF(D86=0,NA(),E86/D86-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C89" s="15">
+        <f>(B86+C86)/2</f>
+        <v/>
+      </c>
+      <c r="D89" s="15">
+        <f>(C86+D86)/2</f>
+        <v/>
+      </c>
+      <c r="E89" s="15">
+        <f>(D86+E86)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C90" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B91" s="12">
+        <f>B81+B86</f>
+        <v/>
+      </c>
+      <c r="C91" s="12">
+        <f>C81+C86</f>
+        <v/>
+      </c>
+      <c r="D91" s="12">
+        <f>D81+D86</f>
+        <v/>
+      </c>
+      <c r="E91" s="12">
+        <f>E81+E86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C92" s="15">
+        <f>C91-B91</f>
+        <v/>
+      </c>
+      <c r="D92" s="15">
+        <f>D91-C91</f>
+        <v/>
+      </c>
+      <c r="E92" s="15">
+        <f>E91-D91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C93" s="14">
+        <f>IF(B91=0,NA(),C91/B91-1)</f>
+        <v/>
+      </c>
+      <c r="D93" s="14">
+        <f>IF(C91=0,NA(),D91/C91-1)</f>
+        <v/>
+      </c>
+      <c r="E93" s="14">
+        <f>IF(D91=0,NA(),E91/D91-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C94" s="15">
+        <f>(B91+C91)/2</f>
+        <v/>
+      </c>
+      <c r="D94" s="15">
+        <f>(C91+D91)/2</f>
+        <v/>
+      </c>
+      <c r="E94" s="15">
+        <f>(D91+E91)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C80" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C79/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D80" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D79/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E80" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E79/'Condensed Financials'!E34)</f>
+      <c r="C95" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D95" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E95" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -956,182 +956,222 @@
         <t>Presented PP&amp;E capex divided by same-period Revenue.</t>
       </text>
     </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
     <comment ref="C82" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="E82" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="0" shapeId="0">
+      <text>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="D83" authorId="0" shapeId="0">
+      <text>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="E83" authorId="0" shapeId="0">
+      <text>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="C87" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D82" authorId="0" shapeId="0">
+    <comment ref="D87" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E82" authorId="0" shapeId="0">
+    <comment ref="E87" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C83" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D83" authorId="0" shapeId="0">
+    <comment ref="D88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E83" authorId="0" shapeId="0">
+    <comment ref="E88" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
+    <comment ref="C89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D84" authorId="0" shapeId="0">
+    <comment ref="D89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E84" authorId="0" shapeId="0">
+    <comment ref="E89" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C85" authorId="0" shapeId="0">
+    <comment ref="C90" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D85" authorId="0" shapeId="0">
+    <comment ref="D90" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E85" authorId="0" shapeId="0">
+    <comment ref="E90" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
+    <comment ref="C92" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D87" authorId="0" shapeId="0">
+    <comment ref="D92" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E87" authorId="0" shapeId="0">
+    <comment ref="E92" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0">
+    <comment ref="C93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D88" authorId="0" shapeId="0">
+    <comment ref="D93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E88" authorId="0" shapeId="0">
+    <comment ref="E93" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C89" authorId="0" shapeId="0">
+    <comment ref="C94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D89" authorId="0" shapeId="0">
+    <comment ref="D94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E89" authorId="0" shapeId="0">
+    <comment ref="E94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C90" authorId="0" shapeId="0">
+    <comment ref="C95" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D90" authorId="0" shapeId="0">
+    <comment ref="D95" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E90" authorId="0" shapeId="0">
+    <comment ref="E95" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="0" shapeId="0">
+    <comment ref="C97" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D92" authorId="0" shapeId="0">
+    <comment ref="D97" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E92" authorId="0" shapeId="0">
+    <comment ref="E97" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
+    <comment ref="C98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D93" authorId="0" shapeId="0">
+    <comment ref="D98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E93" authorId="0" shapeId="0">
+    <comment ref="E98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
+    <comment ref="C99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D94" authorId="0" shapeId="0">
+    <comment ref="D99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E94" authorId="0" shapeId="0">
+    <comment ref="E99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
+    <comment ref="C100" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D95" authorId="0" shapeId="0">
+    <comment ref="D100" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E100" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -1894,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3773,7 +3813,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C82:E82</t>
+          <t>C87:E87</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -3803,7 +3843,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C83:E83</t>
+          <t>C88:E88</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3833,7 +3873,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C84:E84</t>
+          <t>C89:E89</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -3863,7 +3903,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C85:E85</t>
+          <t>C90:E90</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -3893,7 +3933,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C87:E87</t>
+          <t>C92:E92</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -3923,7 +3963,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C88:E88</t>
+          <t>C93:E93</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -3953,7 +3993,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C89:E89</t>
+          <t>C94:E94</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -3983,7 +4023,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C90:E90</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4013,7 +4053,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C92:E92</t>
+          <t>C97:E97</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4043,7 +4083,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C93:E93</t>
+          <t>C98:E98</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4073,7 +4113,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C94:E94</t>
+          <t>C99:E99</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4103,7 +4143,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C100:E100</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4409,6 +4449,66 @@
       <c r="F86" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>B82:E82</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>B83:E83</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex, revenue_link</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S274"/>
+  <dimension ref="A1:S282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21146,11 +21246,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>C82</t>
+          <t>C87</t>
         </is>
       </c>
       <c r="I206">
-        <f>C81-B81</f>
+        <f>C86-B86</f>
         <v/>
       </c>
       <c r="J206" t="n">
@@ -21222,11 +21322,11 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D82</t>
+          <t>D87</t>
         </is>
       </c>
       <c r="I207">
-        <f>D81-C81</f>
+        <f>D86-C86</f>
         <v/>
       </c>
       <c r="J207" t="n">
@@ -21298,11 +21398,11 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>E82</t>
+          <t>E87</t>
         </is>
       </c>
       <c r="I208">
-        <f>E81-D81</f>
+        <f>E86-D86</f>
         <v/>
       </c>
       <c r="J208" t="n">
@@ -21374,11 +21474,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>C83</t>
+          <t>C88</t>
         </is>
       </c>
       <c r="I209">
-        <f>IF(B81=0,NA(),C81/B81-1)</f>
+        <f>IF(B86=0,NA(),C86/B86-1)</f>
         <v/>
       </c>
       <c r="J209" t="n">
@@ -21455,11 +21555,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>D83</t>
+          <t>D88</t>
         </is>
       </c>
       <c r="I210">
-        <f>IF(C81=0,NA(),D81/C81-1)</f>
+        <f>IF(C86=0,NA(),D86/C86-1)</f>
         <v/>
       </c>
       <c r="J210" t="n">
@@ -21536,11 +21636,11 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>E83</t>
+          <t>E88</t>
         </is>
       </c>
       <c r="I211">
-        <f>IF(D81=0,NA(),E81/D81-1)</f>
+        <f>IF(D86=0,NA(),E86/D86-1)</f>
         <v/>
       </c>
       <c r="J211" t="n">
@@ -21617,11 +21717,11 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>C84</t>
+          <t>C89</t>
         </is>
       </c>
       <c r="I212">
-        <f>(B81+C81)/2</f>
+        <f>(B86+C86)/2</f>
         <v/>
       </c>
       <c r="J212" t="n">
@@ -21693,11 +21793,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>D84</t>
+          <t>D89</t>
         </is>
       </c>
       <c r="I213">
-        <f>(C81+D81)/2</f>
+        <f>(C86+D86)/2</f>
         <v/>
       </c>
       <c r="J213" t="n">
@@ -21769,11 +21869,11 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>E84</t>
+          <t>E89</t>
         </is>
       </c>
       <c r="I214">
-        <f>(D81+E81)/2</f>
+        <f>(D86+E86)/2</f>
         <v/>
       </c>
       <c r="J214" t="n">
@@ -21845,11 +21945,11 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>C85</t>
+          <t>C90</t>
         </is>
       </c>
       <c r="I215">
-        <f>IF('Condensed Financials'!C34=0,NA(),C84/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J215" t="n">
@@ -21926,11 +22026,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>D85</t>
+          <t>D90</t>
         </is>
       </c>
       <c r="I216">
-        <f>IF('Condensed Financials'!D34=0,NA(),D84/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J216" t="n">
@@ -22007,11 +22107,11 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>E85</t>
+          <t>E90</t>
         </is>
       </c>
       <c r="I217">
-        <f>IF('Condensed Financials'!E34=0,NA(),E84/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J217" t="n">
@@ -22088,11 +22188,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C87</t>
+          <t>C92</t>
         </is>
       </c>
       <c r="I218">
-        <f>C86-B86</f>
+        <f>C91-B91</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -22164,11 +22264,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D87</t>
+          <t>D92</t>
         </is>
       </c>
       <c r="I219">
-        <f>D86-C86</f>
+        <f>D91-C91</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -22240,11 +22340,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E87</t>
+          <t>E92</t>
         </is>
       </c>
       <c r="I220">
-        <f>E86-D86</f>
+        <f>E91-D91</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -22316,11 +22416,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C88</t>
+          <t>C93</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <f>IF(B91=0,NA(),C91/B91-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -22397,11 +22497,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D88</t>
+          <t>D93</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <f>IF(C91=0,NA(),D91/C91-1)</f>
         <v/>
       </c>
       <c r="J222" t="e">
@@ -22478,11 +22578,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E88</t>
+          <t>E93</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D86=0,NA(),E86/D86-1)</f>
+        <f>IF(D91=0,NA(),E91/D91-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -22559,11 +22659,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C89</t>
+          <t>C94</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B86+C86)/2</f>
+        <f>(B91+C91)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -22635,11 +22735,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D89</t>
+          <t>D94</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C86+D86)/2</f>
+        <f>(C91+D91)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -22711,11 +22811,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E89</t>
+          <t>E94</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D86+E86)/2</f>
+        <f>(D91+E91)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -22787,11 +22887,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C90</t>
+          <t>C95</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -22868,11 +22968,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D90</t>
+          <t>D95</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -22949,11 +23049,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E90</t>
+          <t>E95</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -23030,11 +23130,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C92</t>
+          <t>C97</t>
         </is>
       </c>
       <c r="I230">
-        <f>C91-B91</f>
+        <f>C96-B96</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -23106,11 +23206,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D92</t>
+          <t>D97</t>
         </is>
       </c>
       <c r="I231">
-        <f>D91-C91</f>
+        <f>D96-C96</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -23182,11 +23282,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E92</t>
+          <t>E97</t>
         </is>
       </c>
       <c r="I232">
-        <f>E91-D91</f>
+        <f>E96-D96</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -23258,11 +23358,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C93</t>
+          <t>C98</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
+        <f>IF(B96=0,NA(),C96/B96-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -23339,11 +23439,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D93</t>
+          <t>D98</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
+        <f>IF(C96=0,NA(),D96/C96-1)</f>
         <v/>
       </c>
       <c r="J234" t="n">
@@ -23420,11 +23520,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E93</t>
+          <t>E98</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
+        <f>IF(D96=0,NA(),E96/D96-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -23501,11 +23601,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C94</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B91+C91)/2</f>
+        <f>(B96+C96)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -23577,11 +23677,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D94</t>
+          <t>D99</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C91+D91)/2</f>
+        <f>(C96+D96)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -23653,11 +23753,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E94</t>
+          <t>E99</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D91+E91)/2</f>
+        <f>(D96+E96)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -23729,11 +23829,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C95</t>
+          <t>C100</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C99/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -23810,11 +23910,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D95</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D99/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -23891,11 +23991,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E95</t>
+          <t>E100</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E99/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -26504,6 +26604,654 @@
         <v>3</v>
       </c>
       <c r="S274" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20230129</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>274</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>B82</t>
+        </is>
+      </c>
+      <c r="I275">
+        <f>B81-B77</f>
+        <v/>
+      </c>
+      <c r="J275" t="n">
+        <v>327806</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230129</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>124</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20240128</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>275</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>C82</t>
+        </is>
+      </c>
+      <c r="I276">
+        <f>C81-C77</f>
+        <v/>
+      </c>
+      <c r="J276" t="n">
+        <v>1644299</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240128</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>124</v>
+      </c>
+      <c r="R276" t="n">
+        <v>1</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20250202</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>276</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D82</t>
+        </is>
+      </c>
+      <c r="I277">
+        <f>D81-D77</f>
+        <v/>
+      </c>
+      <c r="J277" t="n">
+        <v>1583481</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250202</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>124</v>
+      </c>
+      <c r="R277" t="n">
+        <v>2</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20260201</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>277</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>E82</t>
+        </is>
+      </c>
+      <c r="I278">
+        <f>E81-E77</f>
+        <v/>
+      </c>
+      <c r="J278" t="n">
+        <v>921675</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>ppe_capex__20260201</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>124</v>
+      </c>
+      <c r="R278" t="n">
+        <v>3</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue__20230129</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>278</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex_to_revenue.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>B83</t>
+        </is>
+      </c>
+      <c r="I279">
+        <f>IF('Condensed Financials'!B34=0,NA(),B82/'Condensed Financials'!B34)</f>
+        <v/>
+      </c>
+      <c r="J279" t="n">
+        <v>0.04041739380887879</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20230129,revenue_link__20230129</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>125</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue__20240128</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>279</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex_to_revenue.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>C83</t>
+        </is>
+      </c>
+      <c r="I280">
+        <f>IF('Condensed Financials'!C34=0,NA(),C82/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="J280" t="n">
+        <v>0.1709378812006473</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20240128,revenue_link__20240128</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>125</v>
+      </c>
+      <c r="R280" t="n">
+        <v>1</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue__20250202</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>280</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex_to_revenue.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="I281">
+        <f>IF('Condensed Financials'!D34=0,NA(),D82/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="J281" t="n">
+        <v>0.1495525270477514</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20250202,revenue_link__20250202</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>125</v>
+      </c>
+      <c r="R281" t="n">
+        <v>2</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue__20260201</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>281</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>capex.cash_after_ppe_capex_to_revenue.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>E83</t>
+        </is>
+      </c>
+      <c r="I282">
+        <f>IF('Condensed Financials'!E34=0,NA(),E82/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+      <c r="J282" t="n">
+        <v>0.08301433898366148</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex__20260201,revenue_link__20260201</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>125</v>
+      </c>
+      <c r="R282" t="n">
+        <v>3</v>
+      </c>
+      <c r="S282" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -29588,7 +30336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -31072,136 +31820,114 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>OPERATING CASH AFTER PP&amp;E CAPEX</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Operating Cash Flow (reported)</t>
         </is>
       </c>
       <c r="B81" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B27</f>
         <v/>
       </c>
       <c r="C81" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C27</f>
         <v/>
       </c>
       <c r="D81" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D27</f>
         <v/>
       </c>
       <c r="E81" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E27</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="B82" s="15">
+        <f>B81-B77</f>
+        <v/>
       </c>
       <c r="C82" s="15">
-        <f>C81-B81</f>
+        <f>C81-C77</f>
         <v/>
       </c>
       <c r="D82" s="15">
-        <f>D81-C81</f>
+        <f>D81-D77</f>
         <v/>
       </c>
       <c r="E82" s="15">
-        <f>E81-D81</f>
+        <f>E81-E77</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="B83" s="14">
+        <f>IF('Condensed Financials'!B34=0,NA(),B82/'Condensed Financials'!B34)</f>
+        <v/>
       </c>
       <c r="C83" s="14">
-        <f>IF(B81=0,NA(),C81/B81-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C82/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D83" s="14">
-        <f>IF(C81=0,NA(),D81/C81-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D82/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E83" s="14">
-        <f>IF(D81=0,NA(),E81/D81-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C84" s="15">
-        <f>(B81+C81)/2</f>
-        <v/>
-      </c>
-      <c r="D84" s="15">
-        <f>(C81+D81)/2</f>
-        <v/>
-      </c>
-      <c r="E84" s="15">
-        <f>(D81+E81)/2</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF('Condensed Financials'!E34=0,NA(),E82/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C85" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C84/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D85" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D84/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E85" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E84/'Condensed Financials'!E34)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B86" s="12">
-        <f>'Balance Sheet'!B23</f>
+        <f>'Balance Sheet'!B22</f>
         <v/>
       </c>
       <c r="C86" s="12">
-        <f>'Balance Sheet'!C23</f>
+        <f>'Balance Sheet'!C22</f>
         <v/>
       </c>
       <c r="D86" s="12">
-        <f>'Balance Sheet'!D23</f>
+        <f>'Balance Sheet'!D22</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>'Balance Sheet'!E23</f>
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Goodwill</t>
         </is>
       </c>
       <c r="C87" s="15">
@@ -31220,7 +31946,7 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Goodwill Growth</t>
         </is>
       </c>
       <c r="C88" s="14">
@@ -31239,7 +31965,7 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C89" s="15">
@@ -31258,7 +31984,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C90" s="14">
@@ -31277,30 +32003,30 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Intangible Assets</t>
         </is>
       </c>
       <c r="B91" s="12">
-        <f>B81+B86</f>
+        <f>'Balance Sheet'!B23</f>
         <v/>
       </c>
       <c r="C91" s="12">
-        <f>C81+C86</f>
+        <f>'Balance Sheet'!C23</f>
         <v/>
       </c>
       <c r="D91" s="12">
-        <f>D81+D86</f>
+        <f>'Balance Sheet'!D23</f>
         <v/>
       </c>
       <c r="E91" s="12">
-        <f>E81+E86</f>
+        <f>'Balance Sheet'!E23</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Change in Intangible Assets</t>
         </is>
       </c>
       <c r="C92" s="15">
@@ -31319,7 +32045,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Intangible Assets Growth</t>
         </is>
       </c>
       <c r="C93" s="14">
@@ -31338,7 +32064,7 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C94" s="15">
@@ -31357,7 +32083,7 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C95" s="14">
@@ -31370,6 +32096,105 @@
       </c>
       <c r="E95" s="14">
         <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B96" s="12">
+        <f>B86+B91</f>
+        <v/>
+      </c>
+      <c r="C96" s="12">
+        <f>C86+C91</f>
+        <v/>
+      </c>
+      <c r="D96" s="12">
+        <f>D86+D91</f>
+        <v/>
+      </c>
+      <c r="E96" s="12">
+        <f>E86+E91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C97" s="15">
+        <f>C96-B96</f>
+        <v/>
+      </c>
+      <c r="D97" s="15">
+        <f>D96-C96</f>
+        <v/>
+      </c>
+      <c r="E97" s="15">
+        <f>E96-D96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C98" s="14">
+        <f>IF(B96=0,NA(),C96/B96-1)</f>
+        <v/>
+      </c>
+      <c r="D98" s="14">
+        <f>IF(C96=0,NA(),D96/C96-1)</f>
+        <v/>
+      </c>
+      <c r="E98" s="14">
+        <f>IF(D96=0,NA(),E96/D96-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C99" s="15">
+        <f>(B96+C96)/2</f>
+        <v/>
+      </c>
+      <c r="D99" s="15">
+        <f>(C96+D96)/2</f>
+        <v/>
+      </c>
+      <c r="E99" s="15">
+        <f>(D96+E96)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C100" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C99/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D100" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D99/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E100" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E99/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -996,182 +996,242 @@
         <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
     <comment ref="C87" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="D87" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="E87" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="C88" authorId="0" shapeId="0">
+      <text>
+        <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="D88" authorId="0" shapeId="0">
+      <text>
+        <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="E88" authorId="0" shapeId="0">
+      <text>
+        <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="C91" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="D91" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="E91" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D87" authorId="0" shapeId="0">
+    <comment ref="D95" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E87" authorId="0" shapeId="0">
+    <comment ref="E95" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0">
+    <comment ref="C96" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D88" authorId="0" shapeId="0">
+    <comment ref="D96" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E88" authorId="0" shapeId="0">
+    <comment ref="E96" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C89" authorId="0" shapeId="0">
+    <comment ref="C97" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D89" authorId="0" shapeId="0">
+    <comment ref="D97" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E89" authorId="0" shapeId="0">
+    <comment ref="E97" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C90" authorId="0" shapeId="0">
+    <comment ref="C98" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D90" authorId="0" shapeId="0">
+    <comment ref="D98" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E90" authorId="0" shapeId="0">
+    <comment ref="E98" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="0" shapeId="0">
+    <comment ref="C100" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D92" authorId="0" shapeId="0">
+    <comment ref="D100" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E92" authorId="0" shapeId="0">
+    <comment ref="E100" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D93" authorId="0" shapeId="0">
+    <comment ref="D101" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E93" authorId="0" shapeId="0">
+    <comment ref="E101" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
+    <comment ref="C102" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D94" authorId="0" shapeId="0">
+    <comment ref="D102" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E94" authorId="0" shapeId="0">
+    <comment ref="E102" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
+    <comment ref="C103" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D95" authorId="0" shapeId="0">
+    <comment ref="D103" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E103" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
+    <comment ref="C105" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D97" authorId="0" shapeId="0">
+    <comment ref="D105" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E97" authorId="0" shapeId="0">
+    <comment ref="E105" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
+    <comment ref="C106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D98" authorId="0" shapeId="0">
+    <comment ref="D106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E98" authorId="0" shapeId="0">
+    <comment ref="E106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C99" authorId="0" shapeId="0">
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0">
+    <comment ref="D107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0">
+    <comment ref="E107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D100" authorId="0" shapeId="0">
+    <comment ref="D108" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E100" authorId="0" shapeId="0">
+    <comment ref="E108" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -1994,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3873,7 +3933,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C87:E87</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -3903,7 +3963,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C88:E88</t>
+          <t>C96:E96</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3933,7 +3993,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C89:E89</t>
+          <t>C97:E97</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -3963,7 +4023,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C90:E90</t>
+          <t>C98:E98</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -3993,7 +4053,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C92:E92</t>
+          <t>C100:E100</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4023,7 +4083,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C93:E93</t>
+          <t>C101:E101</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4053,7 +4113,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C94:E94</t>
+          <t>C102:E102</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4083,7 +4143,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C103:E103</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4113,7 +4173,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C97:E97</t>
+          <t>C105:E105</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4143,7 +4203,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C98:E98</t>
+          <t>C106:E106</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4173,7 +4233,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C99:E99</t>
+          <t>C107:E107</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4203,7 +4263,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C100:E100</t>
+          <t>C108:E108</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4659,6 +4719,96 @@
       <c r="F91" s="10" t="inlineStr">
         <is>
           <t>operating_cash_flow_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>B87:E87</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>B88:E88</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>B91:E91</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex, acquisition_cash_outflow</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S294"/>
+  <dimension ref="A1:S306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22368,11 +22518,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C87</t>
+          <t>C95</t>
         </is>
       </c>
       <c r="I218">
-        <f>C86-B86</f>
+        <f>C94-B94</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -22444,11 +22594,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D87</t>
+          <t>D95</t>
         </is>
       </c>
       <c r="I219">
-        <f>D86-C86</f>
+        <f>D94-C94</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -22520,11 +22670,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E87</t>
+          <t>E95</t>
         </is>
       </c>
       <c r="I220">
-        <f>E86-D86</f>
+        <f>E94-D94</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -22596,11 +22746,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C88</t>
+          <t>C96</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <f>IF(B94=0,NA(),C94/B94-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -22677,11 +22827,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D88</t>
+          <t>D96</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <f>IF(C94=0,NA(),D94/C94-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -22758,11 +22908,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E88</t>
+          <t>E96</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D86=0,NA(),E86/D86-1)</f>
+        <f>IF(D94=0,NA(),E94/D94-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -22839,11 +22989,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C89</t>
+          <t>C97</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B86+C86)/2</f>
+        <f>(B94+C94)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -22915,11 +23065,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D89</t>
+          <t>D97</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C86+D86)/2</f>
+        <f>(C94+D94)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -22991,11 +23141,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E89</t>
+          <t>E97</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D86+E86)/2</f>
+        <f>(D94+E94)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -23067,11 +23217,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C90</t>
+          <t>C98</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C97/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -23148,11 +23298,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D90</t>
+          <t>D98</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D97/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -23229,11 +23379,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E90</t>
+          <t>E98</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E97/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -23310,11 +23460,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C92</t>
+          <t>C100</t>
         </is>
       </c>
       <c r="I230">
-        <f>C91-B91</f>
+        <f>C99-B99</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -23386,11 +23536,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D92</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I231">
-        <f>D91-C91</f>
+        <f>D99-C99</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -23462,11 +23612,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E92</t>
+          <t>E100</t>
         </is>
       </c>
       <c r="I232">
-        <f>E91-D91</f>
+        <f>E99-D99</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -23538,11 +23688,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C93</t>
+          <t>C101</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
+        <f>IF(B99=0,NA(),C99/B99-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -23619,11 +23769,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D93</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
+        <f>IF(C99=0,NA(),D99/C99-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -23700,11 +23850,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E93</t>
+          <t>E101</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
+        <f>IF(D99=0,NA(),E99/D99-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -23781,11 +23931,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C94</t>
+          <t>C102</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B91+C91)/2</f>
+        <f>(B99+C99)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -23857,11 +24007,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D94</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C91+D91)/2</f>
+        <f>(C99+D99)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -23933,11 +24083,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E94</t>
+          <t>E102</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D91+E91)/2</f>
+        <f>(D99+E99)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -24009,11 +24159,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C95</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C102/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -24090,11 +24240,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D95</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D102/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -24171,11 +24321,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E95</t>
+          <t>E103</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E102/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -24252,11 +24402,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C97</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="I242">
-        <f>C96-B96</f>
+        <f>C104-B104</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -24328,11 +24478,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D97</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I243">
-        <f>D96-C96</f>
+        <f>D104-C104</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -24404,11 +24554,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E97</t>
+          <t>E105</t>
         </is>
       </c>
       <c r="I244">
-        <f>E96-D96</f>
+        <f>E104-D104</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -24480,11 +24630,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C98</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B96=0,NA(),C96/B96-1)</f>
+        <f>IF(B104=0,NA(),C104/B104-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -24561,11 +24711,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D98</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C96=0,NA(),D96/C96-1)</f>
+        <f>IF(C104=0,NA(),D104/C104-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -24642,11 +24792,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E98</t>
+          <t>E106</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D96=0,NA(),E96/D96-1)</f>
+        <f>IF(D104=0,NA(),E104/D104-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -24723,11 +24873,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B96+C96)/2</f>
+        <f>(B104+C104)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -24799,11 +24949,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D99</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C96+D96)/2</f>
+        <f>(C104+D104)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -24875,11 +25025,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E99</t>
+          <t>E107</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D96+E96)/2</f>
+        <f>(D104+E104)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -24951,11 +25101,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C99/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C107/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -25032,11 +25182,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D99/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D107/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -25113,11 +25263,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E100</t>
+          <t>E108</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E99/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E107/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -28374,6 +28524,958 @@
         <v>3</v>
       </c>
       <c r="S294" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20230129</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>294</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_outflow.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>B87</t>
+        </is>
+      </c>
+      <c r="I295">
+        <f>-B86</f>
+        <v/>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow = −(reported acquisition, net of cash acquired).|Do not apply absolute value; keep the −reported sign convention consistently.|Net-of-acquired-cash reporting is retained as filed; explicit zeros remain valid.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>129</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20240128</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>295</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_outflow.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>C87</t>
+        </is>
+      </c>
+      <c r="I296">
+        <f>-C86</f>
+        <v/>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow = −(reported acquisition, net of cash acquired).|Do not apply absolute value; keep the −reported sign convention consistently.|Net-of-acquired-cash reporting is retained as filed; explicit zeros remain valid.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>129</v>
+      </c>
+      <c r="R296" t="n">
+        <v>1</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20250202</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>296</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_outflow.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D87</t>
+        </is>
+      </c>
+      <c r="I297">
+        <f>-D86</f>
+        <v/>
+      </c>
+      <c r="J297" t="n">
+        <v>154146</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow = −(reported acquisition, net of cash acquired).|Do not apply absolute value; keep the −reported sign convention consistently.|Net-of-acquired-cash reporting is retained as filed; explicit zeros remain valid.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>129</v>
+      </c>
+      <c r="R297" t="n">
+        <v>2</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20260201</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>297</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Presented as −reported acquisition cash, net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_outflow.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>E87</t>
+        </is>
+      </c>
+      <c r="I298">
+        <f>-E86</f>
+        <v/>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow = −(reported acquisition, net of cash acquired).|Do not apply absolute value; keep the −reported sign convention consistently.|Net-of-acquired-cash reporting is retained as filed; explicit zeros remain valid.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>129</v>
+      </c>
+      <c r="R298" t="n">
+        <v>3</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue__20230129</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>298</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_to_revenue.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>B88</t>
+        </is>
+      </c>
+      <c r="I299">
+        <f>IF('Condensed Financials'!B34=0,NA(),B87/'Condensed Financials'!B34)</f>
+        <v/>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20230129,revenue_link__20230129</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue uses the −reported net-of-acquired-cash presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>130</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue__20240128</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>299</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_to_revenue.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>C88</t>
+        </is>
+      </c>
+      <c r="I300">
+        <f>IF('Condensed Financials'!C34=0,NA(),C87/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20240128,revenue_link__20240128</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue uses the −reported net-of-acquired-cash presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>130</v>
+      </c>
+      <c r="R300" t="n">
+        <v>1</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue__20250202</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>300</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_to_revenue.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="I301">
+        <f>IF('Condensed Financials'!D34=0,NA(),D87/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="J301" t="n">
+        <v>0.01455838360820413</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20250202,revenue_link__20250202</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue uses the −reported net-of-acquired-cash presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>130</v>
+      </c>
+      <c r="R301" t="n">
+        <v>2</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue__20260201</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>301</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow divided by same-period Revenue. Reported net of cash acquired. Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>acquisition_cash.acquisition_cash_to_revenue.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>E88</t>
+        </is>
+      </c>
+      <c r="I302">
+        <f>IF('Condensed Financials'!E34=0,NA(),E87/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow__20260201,revenue_link__20260201</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue uses the −reported net-of-acquired-cash presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>acquisition_cash_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>130</v>
+      </c>
+      <c r="R302" t="n">
+        <v>3</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions__20230129</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>302</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>acquisition_cash.cash_after_ppe_capex_and_acquisitions.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>B91</t>
+        </is>
+      </c>
+      <c r="I303">
+        <f>B81-B77-B87</f>
+        <v/>
+      </c>
+      <c r="J303" t="n">
+        <v>327806</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230129,acquisition_cash_outflow__20230129</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions = reported CFO − PP&amp;E capex − acquisition cash outflow.|Acquisition cash is the −reported net-of-acquired-cash line; PP&amp;E capex keeps its established −reported contract.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>131</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions__20240128</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>303</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>acquisition_cash.cash_after_ppe_capex_and_acquisitions.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>C91</t>
+        </is>
+      </c>
+      <c r="I304">
+        <f>C81-C77-C87</f>
+        <v/>
+      </c>
+      <c r="J304" t="n">
+        <v>1644299</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240128,acquisition_cash_outflow__20240128</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions = reported CFO − PP&amp;E capex − acquisition cash outflow.|Acquisition cash is the −reported net-of-acquired-cash line; PP&amp;E capex keeps its established −reported contract.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>131</v>
+      </c>
+      <c r="R304" t="n">
+        <v>1</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions__20250202</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>304</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>acquisition_cash.cash_after_ppe_capex_and_acquisitions.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>D91</t>
+        </is>
+      </c>
+      <c r="I305">
+        <f>D81-D77-D87</f>
+        <v/>
+      </c>
+      <c r="J305" t="n">
+        <v>1429335</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250202,acquisition_cash_outflow__20250202</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions = reported CFO − PP&amp;E capex − acquisition cash outflow.|Acquisition cash is the −reported net-of-acquired-cash line; PP&amp;E capex keeps its established −reported contract.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>131</v>
+      </c>
+      <c r="R305" t="n">
+        <v>2</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions__20260201</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>305</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>acquisition_cash.cash_after_ppe_capex_and_acquisitions.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>acquisition_cash</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>E91</t>
+        </is>
+      </c>
+      <c r="I306">
+        <f>E81-E77-E87</f>
+        <v/>
+      </c>
+      <c r="J306" t="n">
+        <v>921675</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>ppe_capex__20260201,acquisition_cash_outflow__20260201</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions = reported CFO − PP&amp;E capex − acquisition cash outflow.|Acquisition cash is the −reported net-of-acquired-cash line; PP&amp;E capex keeps its established −reported contract.|Mechanical cash-use diagnostic only — not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_and_acquisitions</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>131</v>
+      </c>
+      <c r="R306" t="n">
+        <v>3</v>
+      </c>
+      <c r="S306" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -31458,7 +32560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -33019,304 +34121,412 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>ACQUISITION CASH CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Acquisition, net of cash acquired (reported)</t>
         </is>
       </c>
       <c r="B86" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B12</f>
         <v/>
       </c>
       <c r="C86" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C12</f>
         <v/>
       </c>
       <c r="D86" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D12</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E12</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="B87" s="15">
+        <f>-B86</f>
+        <v/>
       </c>
       <c r="C87" s="15">
-        <f>C86-B86</f>
+        <f>-C86</f>
         <v/>
       </c>
       <c r="D87" s="15">
-        <f>D86-C86</f>
+        <f>-D86</f>
         <v/>
       </c>
       <c r="E87" s="15">
-        <f>E86-D86</f>
+        <f>-E86</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="B88" s="14">
+        <f>IF('Condensed Financials'!B34=0,NA(),B87/'Condensed Financials'!B34)</f>
+        <v/>
       </c>
       <c r="C88" s="14">
-        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C87/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D88" s="14">
-        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D87/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E88" s="14">
-        <f>IF(D86=0,NA(),E86/D86-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C89" s="15">
-        <f>(B86+C86)/2</f>
-        <v/>
-      </c>
-      <c r="D89" s="15">
-        <f>(C86+D86)/2</f>
-        <v/>
-      </c>
-      <c r="E89" s="15">
-        <f>(D86+E86)/2</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF('Condensed Financials'!E34=0,NA(),E87/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C90" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C89/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D90" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D89/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E90" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E89/'Condensed Financials'!E34)</f>
-        <v/>
+          <t>CASH AFTER PP&amp;E CAPEX AND ACQUISITIONS</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B91" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C91" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D91" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E91" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C92" s="15">
-        <f>C91-B91</f>
-        <v/>
-      </c>
-      <c r="D92" s="15">
-        <f>D91-C91</f>
-        <v/>
-      </c>
-      <c r="E92" s="15">
-        <f>E91-D91</f>
-        <v/>
-      </c>
-    </row>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="B91" s="15">
+        <f>B81-B77-B87</f>
+        <v/>
+      </c>
+      <c r="C91" s="15">
+        <f>C81-C77-C87</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>D81-D77-D87</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>E81-E77-E87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C93" s="14">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
-        <v/>
-      </c>
-      <c r="D93" s="14">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
-        <v/>
-      </c>
-      <c r="E93" s="14">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C94" s="15">
-        <f>(B91+C91)/2</f>
-        <v/>
-      </c>
-      <c r="D94" s="15">
-        <f>(C91+D91)/2</f>
-        <v/>
-      </c>
-      <c r="E94" s="15">
-        <f>(D91+E91)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B94" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C94" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D94" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E94" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C95" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C94/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D95" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D94/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E95" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E94/'Condensed Financials'!E34)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C95" s="15">
+        <f>C94-B94</f>
+        <v/>
+      </c>
+      <c r="D95" s="15">
+        <f>D94-C94</f>
+        <v/>
+      </c>
+      <c r="E95" s="15">
+        <f>E94-D94</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B96" s="12">
-        <f>B86+B91</f>
-        <v/>
-      </c>
-      <c r="C96" s="12">
-        <f>C86+C91</f>
-        <v/>
-      </c>
-      <c r="D96" s="12">
-        <f>D86+D91</f>
-        <v/>
-      </c>
-      <c r="E96" s="12">
-        <f>E86+E91</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C96" s="14">
+        <f>IF(B94=0,NA(),C94/B94-1)</f>
+        <v/>
+      </c>
+      <c r="D96" s="14">
+        <f>IF(C94=0,NA(),D94/C94-1)</f>
+        <v/>
+      </c>
+      <c r="E96" s="14">
+        <f>IF(D94=0,NA(),E94/D94-1)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C97" s="15">
-        <f>C96-B96</f>
+        <f>(B94+C94)/2</f>
         <v/>
       </c>
       <c r="D97" s="15">
-        <f>D96-C96</f>
+        <f>(C94+D94)/2</f>
         <v/>
       </c>
       <c r="E97" s="15">
-        <f>E96-D96</f>
+        <f>(D94+E94)/2</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C98" s="14">
-        <f>IF(B96=0,NA(),C96/B96-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C97/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D98" s="14">
-        <f>IF(C96=0,NA(),D96/C96-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D97/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E98" s="14">
-        <f>IF(D96=0,NA(),E96/D96-1)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E97/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C99" s="15">
-        <f>(B96+C96)/2</f>
-        <v/>
-      </c>
-      <c r="D99" s="15">
-        <f>(C96+D96)/2</f>
-        <v/>
-      </c>
-      <c r="E99" s="15">
-        <f>(D96+E96)/2</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B99" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C99" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D99" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E99" s="12">
+        <f>'Balance Sheet'!E23</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C100" s="15">
+        <f>C99-B99</f>
+        <v/>
+      </c>
+      <c r="D100" s="15">
+        <f>D99-C99</f>
+        <v/>
+      </c>
+      <c r="E100" s="15">
+        <f>E99-D99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C101" s="14">
+        <f>IF(B99=0,NA(),C99/B99-1)</f>
+        <v/>
+      </c>
+      <c r="D101" s="14">
+        <f>IF(C99=0,NA(),D99/C99-1)</f>
+        <v/>
+      </c>
+      <c r="E101" s="14">
+        <f>IF(D99=0,NA(),E99/D99-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C102" s="15">
+        <f>(B99+C99)/2</f>
+        <v/>
+      </c>
+      <c r="D102" s="15">
+        <f>(C99+D99)/2</f>
+        <v/>
+      </c>
+      <c r="E102" s="15">
+        <f>(D99+E99)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C103" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C102/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D103" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D102/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E103" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E102/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B104" s="12">
+        <f>B94+B99</f>
+        <v/>
+      </c>
+      <c r="C104" s="12">
+        <f>C94+C99</f>
+        <v/>
+      </c>
+      <c r="D104" s="12">
+        <f>D94+D99</f>
+        <v/>
+      </c>
+      <c r="E104" s="12">
+        <f>E94+E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C105" s="15">
+        <f>C104-B104</f>
+        <v/>
+      </c>
+      <c r="D105" s="15">
+        <f>D104-C104</f>
+        <v/>
+      </c>
+      <c r="E105" s="15">
+        <f>E104-D104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C106" s="14">
+        <f>IF(B104=0,NA(),C104/B104-1)</f>
+        <v/>
+      </c>
+      <c r="D106" s="14">
+        <f>IF(C104=0,NA(),D104/C104-1)</f>
+        <v/>
+      </c>
+      <c r="E106" s="14">
+        <f>IF(D104=0,NA(),E104/D104-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C107" s="15">
+        <f>(B104+C104)/2</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>(C104+D104)/2</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>(D104+E104)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C100" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C99/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D100" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D99/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E100" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E99/'Condensed Financials'!E34)</f>
+      <c r="C108" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C107/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D108" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D107/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E108" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E107/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -1056,182 +1056,242 @@
         <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow (net of cash acquired). Mechanical cash-use diagnostic only; not comprehensive free cash flow, acquisition profitability, purchase-price allocation, or a goodwill roll-forward.</t>
       </text>
     </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
     <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="D95" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="C96" authorId="0" shapeId="0">
+      <text>
+        <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="D96" authorId="0" shapeId="0">
+      <text>
+        <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="E96" authorId="0" shapeId="0">
+      <text>
+        <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="C99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="D99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="E99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+      </text>
+    </comment>
+    <comment ref="C103" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D95" authorId="0" shapeId="0">
+    <comment ref="D103" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E103" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C96" authorId="0" shapeId="0">
+    <comment ref="C104" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D96" authorId="0" shapeId="0">
+    <comment ref="D104" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E96" authorId="0" shapeId="0">
+    <comment ref="E104" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
+    <comment ref="C105" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D97" authorId="0" shapeId="0">
+    <comment ref="D105" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E97" authorId="0" shapeId="0">
+    <comment ref="E105" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
+    <comment ref="C106" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D98" authorId="0" shapeId="0">
+    <comment ref="D106" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E98" authorId="0" shapeId="0">
+    <comment ref="E106" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D100" authorId="0" shapeId="0">
+    <comment ref="D108" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E100" authorId="0" shapeId="0">
+    <comment ref="E108" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
+    <comment ref="C109" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D101" authorId="0" shapeId="0">
+    <comment ref="D109" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E101" authorId="0" shapeId="0">
+    <comment ref="E109" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C102" authorId="0" shapeId="0">
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0">
+    <comment ref="D110" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0">
+    <comment ref="E110" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
+    <comment ref="C111" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0">
+    <comment ref="D111" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0">
+    <comment ref="E111" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="C113" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D105" authorId="0" shapeId="0">
+    <comment ref="D113" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E105" authorId="0" shapeId="0">
+    <comment ref="E113" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0">
+    <comment ref="C114" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0">
+    <comment ref="D114" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0">
+    <comment ref="E114" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
+    <comment ref="C115" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D107" authorId="0" shapeId="0">
+    <comment ref="D115" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E107" authorId="0" shapeId="0">
+    <comment ref="E115" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0">
+    <comment ref="D116" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0">
+    <comment ref="E116" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -2054,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3933,7 +3993,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C103:E103</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -3963,7 +4023,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C96:E96</t>
+          <t>C104:E104</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3993,7 +4053,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C97:E97</t>
+          <t>C105:E105</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4023,7 +4083,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C98:E98</t>
+          <t>C106:E106</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4053,7 +4113,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C100:E100</t>
+          <t>C108:E108</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4083,7 +4143,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C101:E101</t>
+          <t>C109:E109</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4113,7 +4173,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C102:E102</t>
+          <t>C110:E110</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4143,7 +4203,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C103:E103</t>
+          <t>C111:E111</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4173,7 +4233,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C105:E105</t>
+          <t>C113:E113</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4203,7 +4263,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C106:E106</t>
+          <t>C114:E114</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4233,7 +4293,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C107:E107</t>
+          <t>C115:E115</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4263,7 +4323,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C108:E108</t>
+          <t>C116:E116</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4809,6 +4869,96 @@
       <c r="F94" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, acquisition_cash_outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>B95:E95</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>B96:E96</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>B99:E99</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex, acquisition_cash_outflow, share_repurchase_outflow</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S306"/>
+  <dimension ref="A1:S318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22518,11 +22668,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C95</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="I218">
-        <f>C94-B94</f>
+        <f>C102-B102</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -22594,11 +22744,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D95</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I219">
-        <f>D94-C94</f>
+        <f>D102-C102</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -22670,11 +22820,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E95</t>
+          <t>E103</t>
         </is>
       </c>
       <c r="I220">
-        <f>E94-D94</f>
+        <f>E102-D102</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -22746,11 +22896,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C96</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B94=0,NA(),C94/B94-1)</f>
+        <f>IF(B102=0,NA(),C102/B102-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -22827,11 +22977,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D96</t>
+          <t>D104</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C94=0,NA(),D94/C94-1)</f>
+        <f>IF(C102=0,NA(),D102/C102-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -22908,11 +23058,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E96</t>
+          <t>E104</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D94=0,NA(),E94/D94-1)</f>
+        <f>IF(D102=0,NA(),E102/D102-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -22989,11 +23139,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C97</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B94+C94)/2</f>
+        <f>(B102+C102)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -23065,11 +23215,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D97</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C94+D94)/2</f>
+        <f>(C102+D102)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -23141,11 +23291,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E97</t>
+          <t>E105</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D94+E94)/2</f>
+        <f>(D102+E102)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -23217,11 +23367,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C98</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C97/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C105/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -23298,11 +23448,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D98</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D97/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D105/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -23379,11 +23529,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E98</t>
+          <t>E106</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E97/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E105/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -23460,11 +23610,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="I230">
-        <f>C99-B99</f>
+        <f>C107-B107</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -23536,11 +23686,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I231">
-        <f>D99-C99</f>
+        <f>D107-C107</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -23612,11 +23762,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E100</t>
+          <t>E108</t>
         </is>
       </c>
       <c r="I232">
-        <f>E99-D99</f>
+        <f>E107-D107</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -23688,11 +23838,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C101</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B99=0,NA(),C99/B99-1)</f>
+        <f>IF(B107=0,NA(),C107/B107-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -23769,11 +23919,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D101</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C99=0,NA(),D99/C99-1)</f>
+        <f>IF(C107=0,NA(),D107/C107-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -23850,11 +24000,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E101</t>
+          <t>E109</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D99=0,NA(),E99/D99-1)</f>
+        <f>IF(D107=0,NA(),E107/D107-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -23931,11 +24081,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B99+C99)/2</f>
+        <f>(B107+C107)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -24007,11 +24157,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C99+D99)/2</f>
+        <f>(C107+D107)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -24083,11 +24233,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E102</t>
+          <t>E110</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D99+E99)/2</f>
+        <f>(D107+E107)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -24159,11 +24309,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C111</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C102/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C110/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -24240,11 +24390,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D111</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D102/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D110/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -24321,11 +24471,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E103</t>
+          <t>E111</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E102/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E110/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -24402,11 +24552,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C113</t>
         </is>
       </c>
       <c r="I242">
-        <f>C104-B104</f>
+        <f>C112-B112</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -24478,11 +24628,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I243">
-        <f>D104-C104</f>
+        <f>D112-C112</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -24554,11 +24704,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E105</t>
+          <t>E113</t>
         </is>
       </c>
       <c r="I244">
-        <f>E104-D104</f>
+        <f>E112-D112</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -24630,11 +24780,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C114</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B104=0,NA(),C104/B104-1)</f>
+        <f>IF(B112=0,NA(),C112/B112-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -24711,11 +24861,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C104=0,NA(),D104/C104-1)</f>
+        <f>IF(C112=0,NA(),D112/C112-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -24792,11 +24942,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E106</t>
+          <t>E114</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D104=0,NA(),E104/D104-1)</f>
+        <f>IF(D112=0,NA(),E112/D112-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -24873,11 +25023,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C115</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B104+C104)/2</f>
+        <f>(B112+C112)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -24949,11 +25099,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C104+D104)/2</f>
+        <f>(C112+D112)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -25025,11 +25175,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E107</t>
+          <t>E115</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D104+E104)/2</f>
+        <f>(D112+E112)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -25101,11 +25251,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C108</t>
+          <t>C116</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C107/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C115/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -25182,11 +25332,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D116</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D107/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D115/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -25263,11 +25413,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E108</t>
+          <t>E116</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E107/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E115/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -29476,6 +29626,958 @@
         <v>3</v>
       </c>
       <c r="S306" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20230129</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>306</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_outflow.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>B95</t>
+        </is>
+      </c>
+      <c r="I307">
+        <f>-B94</f>
+        <v/>
+      </c>
+      <c r="J307" t="n">
+        <v>444001</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow = −(reported repurchase of common stock).|Do not apply absolute value; keep the −reported sign convention consistently.|This is the reported cash repurchase line only — not total shareholder distributions or dilution effects.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>132</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20240128</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>307</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_outflow.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>C95</t>
+        </is>
+      </c>
+      <c r="I308">
+        <f>-C94</f>
+        <v/>
+      </c>
+      <c r="J308" t="n">
+        <v>558652</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow = −(reported repurchase of common stock).|Do not apply absolute value; keep the −reported sign convention consistently.|This is the reported cash repurchase line only — not total shareholder distributions or dilution effects.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>132</v>
+      </c>
+      <c r="R308" t="n">
+        <v>1</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20250202</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>308</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_outflow.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>D95</t>
+        </is>
+      </c>
+      <c r="I309">
+        <f>-D94</f>
+        <v/>
+      </c>
+      <c r="J309" t="n">
+        <v>1636879</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow = −(reported repurchase of common stock).|Do not apply absolute value; keep the −reported sign convention consistently.|This is the reported cash repurchase line only — not total shareholder distributions or dilution effects.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>132</v>
+      </c>
+      <c r="R309" t="n">
+        <v>2</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20260201</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>309</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Presented as −reported repurchase of common stock. Reported cash repurchase only — not total shareholder distributions, dividends, treasury-stock movements, share-count change, SBC, settlement proceeds, withholding, or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_outflow.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>E95</t>
+        </is>
+      </c>
+      <c r="I310">
+        <f>-E94</f>
+        <v/>
+      </c>
+      <c r="J310" t="n">
+        <v>1178349</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow = −(reported repurchase of common stock).|Do not apply absolute value; keep the −reported sign convention consistently.|This is the reported cash repurchase line only — not total shareholder distributions or dilution effects.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>132</v>
+      </c>
+      <c r="R310" t="n">
+        <v>3</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue__20230129</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>310</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_to_revenue.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>B96</t>
+        </is>
+      </c>
+      <c r="I311">
+        <f>IF('Condensed Financials'!B34=0,NA(),B95/'Condensed Financials'!B34)</f>
+        <v/>
+      </c>
+      <c r="J311" t="n">
+        <v>0.05474385236553325</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20230129,revenue_link__20230129</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue uses the −reported repurchase-of-common-stock presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Reported cash repurchase only — not total shareholder distributions or dilution.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>133</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue__20240128</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>311</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_to_revenue.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>C96</t>
+        </is>
+      </c>
+      <c r="I312">
+        <f>IF('Condensed Financials'!C34=0,NA(),C95/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="J312" t="n">
+        <v>0.05807629221236771</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20240128,revenue_link__20240128</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue uses the −reported repurchase-of-common-stock presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Reported cash repurchase only — not total shareholder distributions or dilution.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>133</v>
+      </c>
+      <c r="R312" t="n">
+        <v>1</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue__20250202</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>312</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_to_revenue.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D96</t>
+        </is>
+      </c>
+      <c r="I313">
+        <f>IF('Condensed Financials'!D34=0,NA(),D95/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="J313" t="n">
+        <v>0.1545957235491908</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20250202,revenue_link__20250202</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue uses the −reported repurchase-of-common-stock presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Reported cash repurchase only — not total shareholder distributions or dilution.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>133</v>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue__20260201</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>313</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow divided by same-period Revenue. Uses the reported repurchase-of-common-stock cash line, not total shareholder distributions or dilution. Mechanical cash-use diagnostic only; not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>share_repurchase.share_repurchase_to_revenue.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>E96</t>
+        </is>
+      </c>
+      <c r="I314">
+        <f>IF('Condensed Financials'!E34=0,NA(),E95/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+      <c r="J314" t="n">
+        <v>0.106132707654063</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow__20260201,revenue_link__20260201</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue uses the −reported repurchase-of-common-stock presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Reported cash repurchase only — not total shareholder distributions or dilution.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>share_repurchase_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>133</v>
+      </c>
+      <c r="R314" t="n">
+        <v>3</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases__20230129</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>314</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>share_repurchase.cash_after_ppe_capex_acquisitions_and_repurchases.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>B99</t>
+        </is>
+      </c>
+      <c r="I315">
+        <f>B81-B77-B87-B95</f>
+        <v/>
+      </c>
+      <c r="J315" t="n">
+        <v>-116195</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230129,acquisition_cash_outflow__20230129,share_repurchase_outflow__20230129</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases = reported CFO − PP&amp;E capex − acquisition cash outflow − share-repurchase outflow.|A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>134</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases__20240128</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>315</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>share_repurchase.cash_after_ppe_capex_acquisitions_and_repurchases.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>C99</t>
+        </is>
+      </c>
+      <c r="I316">
+        <f>C81-C77-C87-C95</f>
+        <v/>
+      </c>
+      <c r="J316" t="n">
+        <v>1085647</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240128,acquisition_cash_outflow__20240128,share_repurchase_outflow__20240128</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases = reported CFO − PP&amp;E capex − acquisition cash outflow − share-repurchase outflow.|A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>134</v>
+      </c>
+      <c r="R316" t="n">
+        <v>1</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases__20250202</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>316</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>share_repurchase.cash_after_ppe_capex_acquisitions_and_repurchases.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D99</t>
+        </is>
+      </c>
+      <c r="I317">
+        <f>D81-D77-D87-D95</f>
+        <v/>
+      </c>
+      <c r="J317" t="n">
+        <v>-207544</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250202,acquisition_cash_outflow__20250202,share_repurchase_outflow__20250202</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases = reported CFO − PP&amp;E capex − acquisition cash outflow − share-repurchase outflow.|A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>134</v>
+      </c>
+      <c r="R317" t="n">
+        <v>2</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases__20260201</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>317</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>share_repurchase.cash_after_ppe_capex_acquisitions_and_repurchases.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>share_repurchase</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>E99</t>
+        </is>
+      </c>
+      <c r="I318">
+        <f>E81-E77-E87-E95</f>
+        <v/>
+      </c>
+      <c r="J318" t="n">
+        <v>-256674</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>ppe_capex__20260201,acquisition_cash_outflow__20260201,share_repurchase_outflow__20260201</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases = reported CFO − PP&amp;E capex − acquisition cash outflow − share-repurchase outflow.|A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding.|Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex_acquisitions_and_repurchases</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>134</v>
+      </c>
+      <c r="R318" t="n">
+        <v>3</v>
+      </c>
+      <c r="S318" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -32560,7 +33662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -34229,304 +35331,412 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>SHARE REPURCHASE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Repurchase of common stock (reported)</t>
         </is>
       </c>
       <c r="B94" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B10</f>
         <v/>
       </c>
       <c r="C94" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C10</f>
         <v/>
       </c>
       <c r="D94" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D10</f>
         <v/>
       </c>
       <c r="E94" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E10</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="B95" s="15">
+        <f>-B94</f>
+        <v/>
       </c>
       <c r="C95" s="15">
-        <f>C94-B94</f>
+        <f>-C94</f>
         <v/>
       </c>
       <c r="D95" s="15">
-        <f>D94-C94</f>
+        <f>-D94</f>
         <v/>
       </c>
       <c r="E95" s="15">
-        <f>E94-D94</f>
+        <f>-E94</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="B96" s="14">
+        <f>IF('Condensed Financials'!B34=0,NA(),B95/'Condensed Financials'!B34)</f>
+        <v/>
       </c>
       <c r="C96" s="14">
-        <f>IF(B94=0,NA(),C94/B94-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C95/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D96" s="14">
-        <f>IF(C94=0,NA(),D94/C94-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D95/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E96" s="14">
-        <f>IF(D94=0,NA(),E94/D94-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C97" s="15">
-        <f>(B94+C94)/2</f>
-        <v/>
-      </c>
-      <c r="D97" s="15">
-        <f>(C94+D94)/2</f>
-        <v/>
-      </c>
-      <c r="E97" s="15">
-        <f>(D94+E94)/2</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF('Condensed Financials'!E34=0,NA(),E95/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C98" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C97/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D98" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D97/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E98" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E97/'Condensed Financials'!E34)</f>
-        <v/>
+          <t>CASH AFTER PP&amp;E CAPEX, ACQUISITIONS AND REPURCHASES</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B99" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C99" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D99" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E99" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C100" s="15">
-        <f>C99-B99</f>
-        <v/>
-      </c>
-      <c r="D100" s="15">
-        <f>D99-C99</f>
-        <v/>
-      </c>
-      <c r="E100" s="15">
-        <f>E99-D99</f>
-        <v/>
-      </c>
-    </row>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="B99" s="15">
+        <f>B81-B77-B87-B95</f>
+        <v/>
+      </c>
+      <c r="C99" s="15">
+        <f>C81-C77-C87-C95</f>
+        <v/>
+      </c>
+      <c r="D99" s="15">
+        <f>D81-D77-D87-D95</f>
+        <v/>
+      </c>
+      <c r="E99" s="15">
+        <f>E81-E77-E87-E95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C101" s="14">
-        <f>IF(B99=0,NA(),C99/B99-1)</f>
-        <v/>
-      </c>
-      <c r="D101" s="14">
-        <f>IF(C99=0,NA(),D99/C99-1)</f>
-        <v/>
-      </c>
-      <c r="E101" s="14">
-        <f>IF(D99=0,NA(),E99/D99-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C102" s="15">
-        <f>(B99+C99)/2</f>
-        <v/>
-      </c>
-      <c r="D102" s="15">
-        <f>(C99+D99)/2</f>
-        <v/>
-      </c>
-      <c r="E102" s="15">
-        <f>(D99+E99)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B102" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C102" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D102" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E102" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C103" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C102/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D103" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D102/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E103" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E102/'Condensed Financials'!E34)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C103" s="15">
+        <f>C102-B102</f>
+        <v/>
+      </c>
+      <c r="D103" s="15">
+        <f>D102-C102</f>
+        <v/>
+      </c>
+      <c r="E103" s="15">
+        <f>E102-D102</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B104" s="12">
-        <f>B94+B99</f>
-        <v/>
-      </c>
-      <c r="C104" s="12">
-        <f>C94+C99</f>
-        <v/>
-      </c>
-      <c r="D104" s="12">
-        <f>D94+D99</f>
-        <v/>
-      </c>
-      <c r="E104" s="12">
-        <f>E94+E99</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C104" s="14">
+        <f>IF(B102=0,NA(),C102/B102-1)</f>
+        <v/>
+      </c>
+      <c r="D104" s="14">
+        <f>IF(C102=0,NA(),D102/C102-1)</f>
+        <v/>
+      </c>
+      <c r="E104" s="14">
+        <f>IF(D102=0,NA(),E102/D102-1)</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C105" s="15">
-        <f>C104-B104</f>
+        <f>(B102+C102)/2</f>
         <v/>
       </c>
       <c r="D105" s="15">
-        <f>D104-C104</f>
+        <f>(C102+D102)/2</f>
         <v/>
       </c>
       <c r="E105" s="15">
-        <f>E104-D104</f>
+        <f>(D102+E102)/2</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C106" s="14">
-        <f>IF(B104=0,NA(),C104/B104-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C105/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D106" s="14">
-        <f>IF(C104=0,NA(),D104/C104-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D105/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E106" s="14">
-        <f>IF(D104=0,NA(),E104/D104-1)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E105/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C107" s="15">
-        <f>(B104+C104)/2</f>
-        <v/>
-      </c>
-      <c r="D107" s="15">
-        <f>(C104+D104)/2</f>
-        <v/>
-      </c>
-      <c r="E107" s="15">
-        <f>(D104+E104)/2</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B107" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C107" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D107" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E107" s="12">
+        <f>'Balance Sheet'!E23</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C108" s="15">
+        <f>C107-B107</f>
+        <v/>
+      </c>
+      <c r="D108" s="15">
+        <f>D107-C107</f>
+        <v/>
+      </c>
+      <c r="E108" s="15">
+        <f>E107-D107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C109" s="14">
+        <f>IF(B107=0,NA(),C107/B107-1)</f>
+        <v/>
+      </c>
+      <c r="D109" s="14">
+        <f>IF(C107=0,NA(),D107/C107-1)</f>
+        <v/>
+      </c>
+      <c r="E109" s="14">
+        <f>IF(D107=0,NA(),E107/D107-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C110" s="15">
+        <f>(B107+C107)/2</f>
+        <v/>
+      </c>
+      <c r="D110" s="15">
+        <f>(C107+D107)/2</f>
+        <v/>
+      </c>
+      <c r="E110" s="15">
+        <f>(D107+E107)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C111" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C110/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D111" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D110/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E111" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E110/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B112" s="12">
+        <f>B102+B107</f>
+        <v/>
+      </c>
+      <c r="C112" s="12">
+        <f>C102+C107</f>
+        <v/>
+      </c>
+      <c r="D112" s="12">
+        <f>D102+D107</f>
+        <v/>
+      </c>
+      <c r="E112" s="12">
+        <f>E102+E107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C113" s="15">
+        <f>C112-B112</f>
+        <v/>
+      </c>
+      <c r="D113" s="15">
+        <f>D112-C112</f>
+        <v/>
+      </c>
+      <c r="E113" s="15">
+        <f>E112-D112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C114" s="14">
+        <f>IF(B112=0,NA(),C112/B112-1)</f>
+        <v/>
+      </c>
+      <c r="D114" s="14">
+        <f>IF(C112=0,NA(),D112/C112-1)</f>
+        <v/>
+      </c>
+      <c r="E114" s="14">
+        <f>IF(D112=0,NA(),E112/D112-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C115" s="15">
+        <f>(B112+C112)/2</f>
+        <v/>
+      </c>
+      <c r="D115" s="15">
+        <f>(C112+D112)/2</f>
+        <v/>
+      </c>
+      <c r="E115" s="15">
+        <f>(D112+E112)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C108" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C107/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D108" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D107/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E108" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E107/'Condensed Financials'!E34)</f>
+      <c r="C116" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C115/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D116" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D115/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E116" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E115/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -1116,182 +1116,262 @@
         <t>Reported CFO minus PP&amp;E capex minus acquisition cash outflow minus share-repurchase outflow. A negative residual means these selected cash uses exceed reported CFO; it does not identify debt funding. Mechanical cash-use diagnostic only — not comprehensive free cash flow or a complete cash reconciliation.</t>
       </text>
     </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C106" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D106" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E106" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C108" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D108" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E108" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C110" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D110" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E110" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C112" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D112" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E112" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0">
+    <comment ref="D116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0">
+    <comment ref="E116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C104" authorId="0" shapeId="0">
+    <comment ref="C117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0">
+    <comment ref="D117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0">
+    <comment ref="E117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="C118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D105" authorId="0" shapeId="0">
+    <comment ref="D118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E105" authorId="0" shapeId="0">
+    <comment ref="E118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0">
+    <comment ref="C119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0">
+    <comment ref="D119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0">
+    <comment ref="E119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0">
+    <comment ref="D121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0">
+    <comment ref="E121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C109" authorId="0" shapeId="0">
+    <comment ref="C122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D109" authorId="0" shapeId="0">
+    <comment ref="D122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E109" authorId="0" shapeId="0">
+    <comment ref="E122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0">
+    <comment ref="D123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0">
+    <comment ref="E123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C111" authorId="0" shapeId="0">
+    <comment ref="C124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D111" authorId="0" shapeId="0">
+    <comment ref="D124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E111" authorId="0" shapeId="0">
+    <comment ref="E124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C113" authorId="0" shapeId="0">
+    <comment ref="C126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D113" authorId="0" shapeId="0">
+    <comment ref="D126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E113" authorId="0" shapeId="0">
+    <comment ref="E126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C114" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D114" authorId="0" shapeId="0">
+    <comment ref="D127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E114" authorId="0" shapeId="0">
+    <comment ref="E127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C115" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D115" authorId="0" shapeId="0">
+    <comment ref="D128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E115" authorId="0" shapeId="0">
+    <comment ref="E128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D116" authorId="0" shapeId="0">
+    <comment ref="D129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E116" authorId="0" shapeId="0">
+    <comment ref="E129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -2114,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3993,7 +4073,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C103:E103</t>
+          <t>C116:E116</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4023,7 +4103,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C104:E104</t>
+          <t>C117:E117</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -4053,7 +4133,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C105:E105</t>
+          <t>C118:E118</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4083,7 +4163,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C106:E106</t>
+          <t>C119:E119</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4113,7 +4193,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C108:E108</t>
+          <t>C121:E121</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4143,7 +4223,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C109:E109</t>
+          <t>C122:E122</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4173,7 +4253,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C110:E110</t>
+          <t>C123:E123</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4203,7 +4283,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C111:E111</t>
+          <t>C124:E124</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4233,7 +4313,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C113:E113</t>
+          <t>C126:E126</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4263,7 +4343,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C114:E114</t>
+          <t>C127:E127</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4293,7 +4373,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C115:E115</t>
+          <t>C128:E128</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4323,7 +4403,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C116:E116</t>
+          <t>C129:E129</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4959,6 +5039,126 @@
       <c r="F97" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, acquisition_cash_outflow, share_repurchase_outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>B106:E106</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>B108:E108</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>B110:E110</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>B112:E112</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S318"/>
+  <dimension ref="A1:S334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22668,11 +22868,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C116</t>
         </is>
       </c>
       <c r="I218">
-        <f>C102-B102</f>
+        <f>C115-B115</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -22744,11 +22944,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D116</t>
         </is>
       </c>
       <c r="I219">
-        <f>D102-C102</f>
+        <f>D115-C115</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -22820,11 +23020,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E103</t>
+          <t>E116</t>
         </is>
       </c>
       <c r="I220">
-        <f>E102-D102</f>
+        <f>E115-D115</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -22896,11 +23096,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C117</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B102=0,NA(),C102/B102-1)</f>
+        <f>IF(B115=0,NA(),C115/B115-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -22977,11 +23177,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D104</t>
+          <t>D117</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C102=0,NA(),D102/C102-1)</f>
+        <f>IF(C115=0,NA(),D115/C115-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -23058,11 +23258,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E104</t>
+          <t>E117</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D102=0,NA(),E102/D102-1)</f>
+        <f>IF(D115=0,NA(),E115/D115-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -23139,11 +23339,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C118</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B102+C102)/2</f>
+        <f>(B115+C115)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -23215,11 +23415,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C102+D102)/2</f>
+        <f>(C115+D115)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -23291,11 +23491,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E105</t>
+          <t>E118</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D102+E102)/2</f>
+        <f>(D115+E115)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -23367,11 +23567,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C105/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C118/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -23448,11 +23648,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D119</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D105/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D118/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -23529,11 +23729,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E106</t>
+          <t>E119</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E105/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E118/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -23610,11 +23810,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C108</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="I230">
-        <f>C107-B107</f>
+        <f>C120-B120</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -23686,11 +23886,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D121</t>
         </is>
       </c>
       <c r="I231">
-        <f>D107-C107</f>
+        <f>D120-C120</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -23762,11 +23962,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E108</t>
+          <t>E121</t>
         </is>
       </c>
       <c r="I232">
-        <f>E107-D107</f>
+        <f>E120-D120</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -23838,11 +24038,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C109</t>
+          <t>C122</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B107=0,NA(),C107/B107-1)</f>
+        <f>IF(B120=0,NA(),C120/B120-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -23919,11 +24119,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C107=0,NA(),D107/C107-1)</f>
+        <f>IF(C120=0,NA(),D120/C120-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -24000,11 +24200,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E109</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D107=0,NA(),E107/D107-1)</f>
+        <f>IF(D120=0,NA(),E120/D120-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -24081,11 +24281,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C110</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B107+C107)/2</f>
+        <f>(B120+C120)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -24157,11 +24357,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C107+D107)/2</f>
+        <f>(C120+D120)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -24233,11 +24433,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E110</t>
+          <t>E123</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D107+E107)/2</f>
+        <f>(D120+E120)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -24309,11 +24509,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C111</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C110/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C123/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -24390,11 +24590,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D111</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D110/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D123/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -24471,11 +24671,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E111</t>
+          <t>E124</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E110/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E123/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -24552,11 +24752,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C126</t>
         </is>
       </c>
       <c r="I242">
-        <f>C112-B112</f>
+        <f>C125-B125</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -24628,11 +24828,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I243">
-        <f>D112-C112</f>
+        <f>D125-C125</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -24704,11 +24904,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E113</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="I244">
-        <f>E112-D112</f>
+        <f>E125-D125</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -24780,11 +24980,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C127</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B112=0,NA(),C112/B112-1)</f>
+        <f>IF(B125=0,NA(),C125/B125-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -24861,11 +25061,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C112=0,NA(),D112/C112-1)</f>
+        <f>IF(C125=0,NA(),D125/C125-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -24942,11 +25142,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E114</t>
+          <t>E127</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D112=0,NA(),E112/D112-1)</f>
+        <f>IF(D125=0,NA(),E125/D125-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -25023,11 +25223,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C115</t>
+          <t>C128</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B112+C112)/2</f>
+        <f>(B125+C125)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -25099,11 +25299,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C112+D112)/2</f>
+        <f>(C125+D125)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -25175,11 +25375,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E115</t>
+          <t>E128</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D112+E112)/2</f>
+        <f>(D125+E125)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -25251,11 +25451,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C116</t>
+          <t>C129</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C115/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C128/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -25332,11 +25532,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D116</t>
+          <t>D129</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D115/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D128/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -25413,11 +25613,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E116</t>
+          <t>E129</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E115/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E128/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -30578,6 +30778,1282 @@
         <v>3</v>
       </c>
       <c r="S318" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230129</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>318</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>B106</t>
+        </is>
+      </c>
+      <c r="I319">
+        <f>B102+B103+B104+B105</f>
+        <v/>
+      </c>
+      <c r="J319" t="n">
+        <v>-105004</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>135</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240128</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>319</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>C106</t>
+        </is>
+      </c>
+      <c r="I320">
+        <f>C102+C103+C104+C105</f>
+        <v/>
+      </c>
+      <c r="J320" t="n">
+        <v>1089104</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>135</v>
+      </c>
+      <c r="R320" t="n">
+        <v>1</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250202</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>320</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I321">
+        <f>D102+D103+D104+D105</f>
+        <v/>
+      </c>
+      <c r="J321" t="n">
+        <v>-259635</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>135</v>
+      </c>
+      <c r="R321" t="n">
+        <v>2</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20260201</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>321</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>E106</t>
+        </is>
+      </c>
+      <c r="I322">
+        <f>E102+E103+E104+E105</f>
+        <v/>
+      </c>
+      <c r="J322" t="n">
+        <v>-177134</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>135</v>
+      </c>
+      <c r="R322" t="n">
+        <v>3</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20230129</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>322</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="I323">
+        <f>B106-B107</f>
+        <v/>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230129</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>136</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20240128</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>323</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>C108</t>
+        </is>
+      </c>
+      <c r="I324">
+        <f>C106-C107</f>
+        <v/>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240128</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>136</v>
+      </c>
+      <c r="R324" t="n">
+        <v>1</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20250202</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>324</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I325">
+        <f>D106-D107</f>
+        <v/>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250202</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>136</v>
+      </c>
+      <c r="R325" t="n">
+        <v>2</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20260201</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>325</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>E108</t>
+        </is>
+      </c>
+      <c r="I326">
+        <f>E106-E107</f>
+        <v/>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20260201</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>136</v>
+      </c>
+      <c r="R326" t="n">
+        <v>3</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20230129</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>326</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>B110</t>
+        </is>
+      </c>
+      <c r="I327">
+        <f>B109+B106</f>
+        <v/>
+      </c>
+      <c r="J327" t="n">
+        <v>1154867</v>
+      </c>
+      <c r="K327" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230129</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>137</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20240128</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>327</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>C110</t>
+        </is>
+      </c>
+      <c r="I328">
+        <f>C109+C106</f>
+        <v/>
+      </c>
+      <c r="J328" t="n">
+        <v>2243971</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240128</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>137</v>
+      </c>
+      <c r="R328" t="n">
+        <v>1</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20250202</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>328</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I329">
+        <f>D109+D106</f>
+        <v/>
+      </c>
+      <c r="J329" t="n">
+        <v>1984336</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250202</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>137</v>
+      </c>
+      <c r="R329" t="n">
+        <v>2</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20260201</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>329</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>E110</t>
+        </is>
+      </c>
+      <c r="I330">
+        <f>E109+E106</f>
+        <v/>
+      </c>
+      <c r="J330" t="n">
+        <v>1807202</v>
+      </c>
+      <c r="K330" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20260201</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>137</v>
+      </c>
+      <c r="R330" t="n">
+        <v>3</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20230129</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>330</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="I331">
+        <f>B110-B111</f>
+        <v/>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20230129</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>138</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20240128</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>331</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="I332">
+        <f>C110-C111</f>
+        <v/>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20240128</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>138</v>
+      </c>
+      <c r="R332" t="n">
+        <v>1</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20250202</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>332</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I333">
+        <f>D110-D111</f>
+        <v/>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20250202</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>138</v>
+      </c>
+      <c r="R333" t="n">
+        <v>2</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20260201</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>333</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>E112</t>
+        </is>
+      </c>
+      <c r="I334">
+        <f>E110-E111</f>
+        <v/>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20260201</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>138</v>
+      </c>
+      <c r="R334" t="n">
+        <v>3</v>
+      </c>
+      <c r="S334" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -33662,7 +35138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -35439,304 +36915,565 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>CASH ROLL-FORWARD CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Net cash from operating activities (reported)</t>
         </is>
       </c>
       <c r="B102" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B27</f>
         <v/>
       </c>
       <c r="C102" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C27</f>
         <v/>
       </c>
       <c r="D102" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D27</f>
         <v/>
       </c>
       <c r="E102" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E27</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C103" s="15">
-        <f>C102-B102</f>
-        <v/>
-      </c>
-      <c r="D103" s="15">
-        <f>D102-C102</f>
-        <v/>
-      </c>
-      <c r="E103" s="15">
-        <f>E102-D102</f>
+          <t>Net cash from investing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B103" s="12">
+        <f>'Cash Flow Statement'!B13</f>
+        <v/>
+      </c>
+      <c r="C103" s="12">
+        <f>'Cash Flow Statement'!C13</f>
+        <v/>
+      </c>
+      <c r="D103" s="12">
+        <f>'Cash Flow Statement'!D13</f>
+        <v/>
+      </c>
+      <c r="E103" s="12">
+        <f>'Cash Flow Statement'!E13</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C104" s="14">
-        <f>IF(B102=0,NA(),C102/B102-1)</f>
-        <v/>
-      </c>
-      <c r="D104" s="14">
-        <f>IF(C102=0,NA(),D102/C102-1)</f>
-        <v/>
-      </c>
-      <c r="E104" s="14">
-        <f>IF(D102=0,NA(),E102/D102-1)</f>
+          <t>Net cash from financing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B104" s="12">
+        <f>'Cash Flow Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C104" s="12">
+        <f>'Cash Flow Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D104" s="12">
+        <f>'Cash Flow Statement'!D7</f>
+        <v/>
+      </c>
+      <c r="E104" s="12">
+        <f>'Cash Flow Statement'!E7</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C105" s="15">
-        <f>(B102+C102)/2</f>
-        <v/>
-      </c>
-      <c r="D105" s="15">
-        <f>(C102+D102)/2</f>
-        <v/>
-      </c>
-      <c r="E105" s="15">
-        <f>(D102+E102)/2</f>
+          <t>Effect of FX on cash (reported)</t>
+        </is>
+      </c>
+      <c r="B105" s="12">
+        <f>'Cash Flow Statement'!B39</f>
+        <v/>
+      </c>
+      <c r="C105" s="12">
+        <f>'Cash Flow Statement'!C39</f>
+        <v/>
+      </c>
+      <c r="D105" s="12">
+        <f>'Cash Flow Statement'!D39</f>
+        <v/>
+      </c>
+      <c r="E105" s="12">
+        <f>'Cash Flow Statement'!E39</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C106" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C105/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D106" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D105/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E106" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E105/'Condensed Financials'!E34)</f>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="B106" s="15">
+        <f>B102+B103+B104+B105</f>
+        <v/>
+      </c>
+      <c r="C106" s="15">
+        <f>C102+C103+C104+C105</f>
+        <v/>
+      </c>
+      <c r="D106" s="15">
+        <f>D102+D103+D104+D105</f>
+        <v/>
+      </c>
+      <c r="E106" s="15">
+        <f>E102+E103+E104+E105</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Reported cash change</t>
         </is>
       </c>
       <c r="B107" s="12">
-        <f>'Balance Sheet'!B23</f>
+        <f>'Cash Flow Statement'!B40</f>
         <v/>
       </c>
       <c r="C107" s="12">
-        <f>'Balance Sheet'!C23</f>
+        <f>'Cash Flow Statement'!C40</f>
         <v/>
       </c>
       <c r="D107" s="12">
-        <f>'Balance Sheet'!D23</f>
+        <f>'Cash Flow Statement'!D40</f>
         <v/>
       </c>
       <c r="E107" s="12">
-        <f>'Balance Sheet'!E23</f>
+        <f>'Cash Flow Statement'!E40</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="B108" s="15">
+        <f>B106-B107</f>
+        <v/>
       </c>
       <c r="C108" s="15">
-        <f>C107-B107</f>
+        <f>C106-C107</f>
         <v/>
       </c>
       <c r="D108" s="15">
-        <f>D107-C107</f>
+        <f>D106-D107</f>
         <v/>
       </c>
       <c r="E108" s="15">
-        <f>E107-D107</f>
+        <f>E106-E107</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C109" s="14">
-        <f>IF(B107=0,NA(),C107/B107-1)</f>
-        <v/>
-      </c>
-      <c r="D109" s="14">
-        <f>IF(C107=0,NA(),D107/C107-1)</f>
-        <v/>
-      </c>
-      <c r="E109" s="14">
-        <f>IF(D107=0,NA(),E107/D107-1)</f>
+          <t>Cash beginning (reported)</t>
+        </is>
+      </c>
+      <c r="B109" s="12">
+        <f>'Cash Flow Statement'!B37</f>
+        <v/>
+      </c>
+      <c r="C109" s="12">
+        <f>'Cash Flow Statement'!C37</f>
+        <v/>
+      </c>
+      <c r="D109" s="12">
+        <f>'Cash Flow Statement'!D37</f>
+        <v/>
+      </c>
+      <c r="E109" s="12">
+        <f>'Cash Flow Statement'!E37</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="B110" s="15">
+        <f>B109+B106</f>
+        <v/>
       </c>
       <c r="C110" s="15">
-        <f>(B107+C107)/2</f>
+        <f>C109+C106</f>
         <v/>
       </c>
       <c r="D110" s="15">
-        <f>(C107+D107)/2</f>
+        <f>D109+D106</f>
         <v/>
       </c>
       <c r="E110" s="15">
-        <f>(D107+E107)/2</f>
+        <f>E109+E106</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C111" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C110/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D111" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D110/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E111" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E110/'Condensed Financials'!E34)</f>
+          <t>Cash ending (reported)</t>
+        </is>
+      </c>
+      <c r="B111" s="12">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C111" s="12">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D111" s="12">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E111" s="12">
+        <f>'Cash Flow Statement'!E38</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B112" s="12">
-        <f>B102+B107</f>
-        <v/>
-      </c>
-      <c r="C112" s="12">
-        <f>C102+C107</f>
-        <v/>
-      </c>
-      <c r="D112" s="12">
-        <f>D102+D107</f>
-        <v/>
-      </c>
-      <c r="E112" s="12">
-        <f>E102+E107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C113" s="15">
-        <f>C112-B112</f>
-        <v/>
-      </c>
-      <c r="D113" s="15">
-        <f>D112-C112</f>
-        <v/>
-      </c>
-      <c r="E113" s="15">
-        <f>E112-D112</f>
-        <v/>
-      </c>
-    </row>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="B112" s="15">
+        <f>B110-B111</f>
+        <v/>
+      </c>
+      <c r="C112" s="15">
+        <f>C110-C111</f>
+        <v/>
+      </c>
+      <c r="D112" s="15">
+        <f>D110-D111</f>
+        <v/>
+      </c>
+      <c r="E112" s="15">
+        <f>E110-E111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C114" s="14">
-        <f>IF(B112=0,NA(),C112/B112-1)</f>
-        <v/>
-      </c>
-      <c r="D114" s="14">
-        <f>IF(C112=0,NA(),D112/C112-1)</f>
-        <v/>
-      </c>
-      <c r="E114" s="14">
-        <f>IF(D112=0,NA(),E112/D112-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C115" s="15">
-        <f>(B112+C112)/2</f>
-        <v/>
-      </c>
-      <c r="D115" s="15">
-        <f>(C112+D112)/2</f>
-        <v/>
-      </c>
-      <c r="E115" s="15">
-        <f>(D112+E112)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B115" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D115" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E115" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C116" s="15">
+        <f>C115-B115</f>
+        <v/>
+      </c>
+      <c r="D116" s="15">
+        <f>D115-C115</f>
+        <v/>
+      </c>
+      <c r="E116" s="15">
+        <f>E115-D115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C117" s="14">
+        <f>IF(B115=0,NA(),C115/B115-1)</f>
+        <v/>
+      </c>
+      <c r="D117" s="14">
+        <f>IF(C115=0,NA(),D115/C115-1)</f>
+        <v/>
+      </c>
+      <c r="E117" s="14">
+        <f>IF(D115=0,NA(),E115/D115-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C118" s="15">
+        <f>(B115+C115)/2</f>
+        <v/>
+      </c>
+      <c r="D118" s="15">
+        <f>(C115+D115)/2</f>
+        <v/>
+      </c>
+      <c r="E118" s="15">
+        <f>(D115+E115)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C119" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C118/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D119" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D118/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E119" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E118/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B120" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C120" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D120" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E120" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C121" s="15">
+        <f>C120-B120</f>
+        <v/>
+      </c>
+      <c r="D121" s="15">
+        <f>D120-C120</f>
+        <v/>
+      </c>
+      <c r="E121" s="15">
+        <f>E120-D120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C122" s="14">
+        <f>IF(B120=0,NA(),C120/B120-1)</f>
+        <v/>
+      </c>
+      <c r="D122" s="14">
+        <f>IF(C120=0,NA(),D120/C120-1)</f>
+        <v/>
+      </c>
+      <c r="E122" s="14">
+        <f>IF(D120=0,NA(),E120/D120-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C123" s="15">
+        <f>(B120+C120)/2</f>
+        <v/>
+      </c>
+      <c r="D123" s="15">
+        <f>(C120+D120)/2</f>
+        <v/>
+      </c>
+      <c r="E123" s="15">
+        <f>(D120+E120)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C124" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C123/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D124" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D123/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E124" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E123/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B125" s="12">
+        <f>B115+B120</f>
+        <v/>
+      </c>
+      <c r="C125" s="12">
+        <f>C115+C120</f>
+        <v/>
+      </c>
+      <c r="D125" s="12">
+        <f>D115+D120</f>
+        <v/>
+      </c>
+      <c r="E125" s="12">
+        <f>E115+E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C126" s="15">
+        <f>C125-B125</f>
+        <v/>
+      </c>
+      <c r="D126" s="15">
+        <f>D125-C125</f>
+        <v/>
+      </c>
+      <c r="E126" s="15">
+        <f>E125-D125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C127" s="14">
+        <f>IF(B125=0,NA(),C125/B125-1)</f>
+        <v/>
+      </c>
+      <c r="D127" s="14">
+        <f>IF(C125=0,NA(),D125/C125-1)</f>
+        <v/>
+      </c>
+      <c r="E127" s="14">
+        <f>IF(D125=0,NA(),E125/D125-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C128" s="15">
+        <f>(B125+C125)/2</f>
+        <v/>
+      </c>
+      <c r="D128" s="15">
+        <f>(C125+D125)/2</f>
+        <v/>
+      </c>
+      <c r="E128" s="15">
+        <f>(D125+E125)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C116" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C115/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D116" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D115/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E116" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E115/'Condensed Financials'!E34)</f>
+      <c r="C129" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C128/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D129" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D128/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E129" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E128/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -1196,182 +1196,287 @@
         <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="D118" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="E118" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C119" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D119" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E119" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="B120" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C120" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D120" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E120" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C121" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="D121" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="E121" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="C122" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="D122" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="E122" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="D123" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="E123" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D116" authorId="0" shapeId="0">
+    <comment ref="D127" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E116" authorId="0" shapeId="0">
+    <comment ref="E127" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C117" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D117" authorId="0" shapeId="0">
+    <comment ref="D128" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E117" authorId="0" shapeId="0">
+    <comment ref="E128" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C118" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D118" authorId="0" shapeId="0">
+    <comment ref="D129" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E118" authorId="0" shapeId="0">
+    <comment ref="E129" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C119" authorId="0" shapeId="0">
+    <comment ref="C130" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D119" authorId="0" shapeId="0">
+    <comment ref="D130" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E119" authorId="0" shapeId="0">
+    <comment ref="E130" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C121" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D121" authorId="0" shapeId="0">
+    <comment ref="D132" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E121" authorId="0" shapeId="0">
+    <comment ref="E132" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C122" authorId="0" shapeId="0">
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D122" authorId="0" shapeId="0">
+    <comment ref="D133" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E122" authorId="0" shapeId="0">
+    <comment ref="E133" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C123" authorId="0" shapeId="0">
+    <comment ref="C134" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D123" authorId="0" shapeId="0">
+    <comment ref="D134" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E123" authorId="0" shapeId="0">
+    <comment ref="E134" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C124" authorId="0" shapeId="0">
+    <comment ref="C135" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D124" authorId="0" shapeId="0">
+    <comment ref="D135" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E124" authorId="0" shapeId="0">
+    <comment ref="E135" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D126" authorId="0" shapeId="0">
+    <comment ref="D137" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E126" authorId="0" shapeId="0">
+    <comment ref="E137" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C138" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D127" authorId="0" shapeId="0">
+    <comment ref="D138" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E127" authorId="0" shapeId="0">
+    <comment ref="E138" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C139" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D128" authorId="0" shapeId="0">
+    <comment ref="D139" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E128" authorId="0" shapeId="0">
+    <comment ref="E139" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0">
+    <comment ref="C140" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D129" authorId="0" shapeId="0">
+    <comment ref="D140" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E129" authorId="0" shapeId="0">
+    <comment ref="E140" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -2194,7 +2299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4073,7 +4178,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C116:E116</t>
+          <t>C127:E127</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4103,7 +4208,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C117:E117</t>
+          <t>C128:E128</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -4133,7 +4238,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C118:E118</t>
+          <t>C129:E129</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4163,7 +4268,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C119:E119</t>
+          <t>C130:E130</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4193,7 +4298,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C121:E121</t>
+          <t>C132:E132</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4223,7 +4328,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C122:E122</t>
+          <t>C133:E133</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4253,7 +4358,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C123:E123</t>
+          <t>C134:E134</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4283,7 +4388,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C124:E124</t>
+          <t>C135:E135</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4313,7 +4418,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C126:E126</t>
+          <t>C137:E137</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4343,7 +4448,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C127:E127</t>
+          <t>C138:E138</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4373,7 +4478,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C128:E128</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4403,7 +4508,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C129:E129</t>
+          <t>C140:E140</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -5159,6 +5264,186 @@
       <c r="F101" s="10" t="inlineStr">
         <is>
           <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>B118:E118</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>B119:E119</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>B120:E120</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>C121:E121</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>C122:E122</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>C123:E123</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>gross_margin_change, net_operating_expense_burden_change</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S334"/>
+  <dimension ref="A1:S355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22868,11 +23153,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C116</t>
+          <t>C127</t>
         </is>
       </c>
       <c r="I218">
-        <f>C115-B115</f>
+        <f>C126-B126</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -22944,11 +23229,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D116</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I219">
-        <f>D115-C115</f>
+        <f>D126-C126</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -23020,11 +23305,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E116</t>
+          <t>E127</t>
         </is>
       </c>
       <c r="I220">
-        <f>E115-D115</f>
+        <f>E126-D126</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -23096,11 +23381,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C117</t>
+          <t>C128</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B115=0,NA(),C115/B115-1)</f>
+        <f>IF(B126=0,NA(),C126/B126-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -23177,11 +23462,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D117</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C115=0,NA(),D115/C115-1)</f>
+        <f>IF(C126=0,NA(),D126/C126-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -23258,11 +23543,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E117</t>
+          <t>E128</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D115=0,NA(),E115/D115-1)</f>
+        <f>IF(D126=0,NA(),E126/D126-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -23339,11 +23624,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C118</t>
+          <t>C129</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B115+C115)/2</f>
+        <f>(B126+C126)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -23415,11 +23700,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D129</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C115+D115)/2</f>
+        <f>(C126+D126)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -23491,11 +23776,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E118</t>
+          <t>E129</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D115+E115)/2</f>
+        <f>(D126+E126)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -23567,11 +23852,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C130</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C118/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C129/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -23648,11 +23933,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D119</t>
+          <t>D130</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D118/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D129/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -23729,11 +24014,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>E130</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E118/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E129/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -23810,11 +24095,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C132</t>
         </is>
       </c>
       <c r="I230">
-        <f>C120-B120</f>
+        <f>C131-B131</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -23886,11 +24171,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D121</t>
+          <t>D132</t>
         </is>
       </c>
       <c r="I231">
-        <f>D120-C120</f>
+        <f>D131-C131</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -23962,11 +24247,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E121</t>
+          <t>E132</t>
         </is>
       </c>
       <c r="I232">
-        <f>E120-D120</f>
+        <f>E131-D131</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -24038,11 +24323,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C122</t>
+          <t>C133</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B120=0,NA(),C120/B120-1)</f>
+        <f>IF(B131=0,NA(),C131/B131-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -24119,11 +24404,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D133</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C120=0,NA(),D120/C120-1)</f>
+        <f>IF(C131=0,NA(),D131/C131-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -24200,11 +24485,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E122</t>
+          <t>E133</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D120=0,NA(),E120/D120-1)</f>
+        <f>IF(D131=0,NA(),E131/D131-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -24281,11 +24566,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C123</t>
+          <t>C134</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B120+C120)/2</f>
+        <f>(B131+C131)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -24357,11 +24642,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D134</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C120+D120)/2</f>
+        <f>(C131+D131)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -24433,11 +24718,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E123</t>
+          <t>E134</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D120+E120)/2</f>
+        <f>(D131+E131)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -24509,11 +24794,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C124</t>
+          <t>C135</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C123/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C134/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -24590,11 +24875,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D135</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D123/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D134/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -24671,11 +24956,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E124</t>
+          <t>E135</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E123/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E134/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -24752,11 +25037,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C126</t>
+          <t>C137</t>
         </is>
       </c>
       <c r="I242">
-        <f>C125-B125</f>
+        <f>C136-B136</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -24828,11 +25113,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D137</t>
         </is>
       </c>
       <c r="I243">
-        <f>D125-C125</f>
+        <f>D136-C136</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -24904,11 +25189,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E126</t>
+          <t>E137</t>
         </is>
       </c>
       <c r="I244">
-        <f>E125-D125</f>
+        <f>E136-D136</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -24980,11 +25265,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C127</t>
+          <t>C138</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B125=0,NA(),C125/B125-1)</f>
+        <f>IF(B136=0,NA(),C136/B136-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -25061,11 +25346,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D138</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C125=0,NA(),D125/C125-1)</f>
+        <f>IF(C136=0,NA(),D136/C136-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -25142,11 +25427,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E127</t>
+          <t>E138</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D125=0,NA(),E125/D125-1)</f>
+        <f>IF(D136=0,NA(),E136/D136-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -25223,11 +25508,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C128</t>
+          <t>C139</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B125+C125)/2</f>
+        <f>(B136+C136)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -25299,11 +25584,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D139</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C125+D125)/2</f>
+        <f>(C136+D136)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -25375,11 +25660,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E128</t>
+          <t>E139</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D125+E125)/2</f>
+        <f>(D136+E136)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -25451,11 +25736,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C129</t>
+          <t>C140</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C128/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C139/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -25532,11 +25817,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D129</t>
+          <t>D140</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D128/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D139/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -25613,11 +25898,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E129</t>
+          <t>E140</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E128/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E139/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -32054,6 +32339,1647 @@
         <v>3</v>
       </c>
       <c r="S334" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>gross_margin__20230129</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>334</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="I335">
+        <f>IF(B115=0,NA(),B116/B115)</f>
+        <v/>
+      </c>
+      <c r="J335" t="n">
+        <v>0.5538906392908567</v>
+      </c>
+      <c r="K335" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>139</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>gross_margin__20240128</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>335</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>C118</t>
+        </is>
+      </c>
+      <c r="I336">
+        <f>IF(C115=0,NA(),C116/C115)</f>
+        <v/>
+      </c>
+      <c r="J336" t="n">
+        <v>0.583141998806979</v>
+      </c>
+      <c r="K336" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>139</v>
+      </c>
+      <c r="R336" t="n">
+        <v>1</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>gross_margin__20250202</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>336</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I337">
+        <f>IF(D115=0,NA(),D116/D115)</f>
+        <v/>
+      </c>
+      <c r="J337" t="n">
+        <v>0.5922493744407651</v>
+      </c>
+      <c r="K337" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>139</v>
+      </c>
+      <c r="R337" t="n">
+        <v>2</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>gross_margin__20260201</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>337</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>E118</t>
+        </is>
+      </c>
+      <c r="I338">
+        <f>IF(E115=0,NA(),E116/E115)</f>
+        <v/>
+      </c>
+      <c r="J338" t="n">
+        <v>0.566005440167168</v>
+      </c>
+      <c r="K338" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>139</v>
+      </c>
+      <c r="R338" t="n">
+        <v>3</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20230129</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>338</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="I339">
+        <f>IF(B115=0,NA(),B117/B115)</f>
+        <v/>
+      </c>
+      <c r="J339" t="n">
+        <v>0.163788305506504</v>
+      </c>
+      <c r="K339" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>140</v>
+      </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20240128</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>339</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>C119</t>
+        </is>
+      </c>
+      <c r="I340">
+        <f>IF(C115=0,NA(),C117/C115)</f>
+        <v/>
+      </c>
+      <c r="J340" t="n">
+        <v>0.221708531555071</v>
+      </c>
+      <c r="K340" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>140</v>
+      </c>
+      <c r="R340" t="n">
+        <v>1</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20250202</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>340</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>D119</t>
+        </is>
+      </c>
+      <c r="I341">
+        <f>IF(D115=0,NA(),D117/D115)</f>
+        <v/>
+      </c>
+      <c r="J341" t="n">
+        <v>0.2366516038815556</v>
+      </c>
+      <c r="K341" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>140</v>
+      </c>
+      <c r="R341" t="n">
+        <v>2</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20260201</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>341</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>E119</t>
+        </is>
+      </c>
+      <c r="I342">
+        <f>IF(E115=0,NA(),E117/E115)</f>
+        <v/>
+      </c>
+      <c r="J342" t="n">
+        <v>0.1991078666258354</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>140</v>
+      </c>
+      <c r="R342" t="n">
+        <v>3</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20230129</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>342</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="I343">
+        <f>IF(B115=0,NA(),(B116-B117)/B115)</f>
+        <v/>
+      </c>
+      <c r="J343" t="n">
+        <v>0.3901023337843526</v>
+      </c>
+      <c r="K343" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>141</v>
+      </c>
+      <c r="R343" t="n">
+        <v>0</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20240128</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>343</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>C120</t>
+        </is>
+      </c>
+      <c r="I344">
+        <f>IF(C115=0,NA(),(C116-C117)/C115)</f>
+        <v/>
+      </c>
+      <c r="J344" t="n">
+        <v>0.3614334672519081</v>
+      </c>
+      <c r="K344" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>141</v>
+      </c>
+      <c r="R344" t="n">
+        <v>1</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20250202</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>344</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I345">
+        <f>IF(D115=0,NA(),(D116-D117)/D115)</f>
+        <v/>
+      </c>
+      <c r="J345" t="n">
+        <v>0.3555977705592094</v>
+      </c>
+      <c r="K345" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>141</v>
+      </c>
+      <c r="R345" t="n">
+        <v>2</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20260201</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>345</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>E120</t>
+        </is>
+      </c>
+      <c r="I346">
+        <f>IF(E115=0,NA(),(E116-E117)/E115)</f>
+        <v/>
+      </c>
+      <c r="J346" t="n">
+        <v>0.3668975735413327</v>
+      </c>
+      <c r="K346" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>141</v>
+      </c>
+      <c r="R346" t="n">
+        <v>3</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20240128</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>346</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>C121</t>
+        </is>
+      </c>
+      <c r="I347">
+        <f>C118-B118</f>
+        <v/>
+      </c>
+      <c r="J347" t="n">
+        <v>0.02925135951612234</v>
+      </c>
+      <c r="K347" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>gross_margin__20240128,gross_margin__20230129</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q347" t="n">
+        <v>142</v>
+      </c>
+      <c r="R347" t="n">
+        <v>1</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20250202</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>347</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>D121</t>
+        </is>
+      </c>
+      <c r="I348">
+        <f>D118-C118</f>
+        <v/>
+      </c>
+      <c r="J348" t="n">
+        <v>0.009107375633786052</v>
+      </c>
+      <c r="K348" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>gross_margin__20250202,gross_margin__20240128</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q348" t="n">
+        <v>142</v>
+      </c>
+      <c r="R348" t="n">
+        <v>2</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20260201</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>348</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>E121</t>
+        </is>
+      </c>
+      <c r="I349">
+        <f>E118-D118</f>
+        <v/>
+      </c>
+      <c r="J349" t="n">
+        <v>-0.02624393427359706</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>gross_margin__20260201,gross_margin__20250202</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q349" t="n">
+        <v>142</v>
+      </c>
+      <c r="R349" t="n">
+        <v>3</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20240128</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>349</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>C122</t>
+        </is>
+      </c>
+      <c r="I350">
+        <f>C120-B120</f>
+        <v/>
+      </c>
+      <c r="J350" t="n">
+        <v>-0.02866886653244449</v>
+      </c>
+      <c r="K350" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20240128,net_operating_expense_burden__20230129</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>143</v>
+      </c>
+      <c r="R350" t="n">
+        <v>1</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20250202</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>350</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I351">
+        <f>D120-C120</f>
+        <v/>
+      </c>
+      <c r="J351" t="n">
+        <v>-0.005835696692698678</v>
+      </c>
+      <c r="K351" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20250202,net_operating_expense_burden__20240128</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q351" t="n">
+        <v>143</v>
+      </c>
+      <c r="R351" t="n">
+        <v>2</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20260201</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>351</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>E122</t>
+        </is>
+      </c>
+      <c r="I352">
+        <f>E120-D120</f>
+        <v/>
+      </c>
+      <c r="J352" t="n">
+        <v>0.01129980298212324</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20260201,net_operating_expense_burden__20250202</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q352" t="n">
+        <v>143</v>
+      </c>
+      <c r="R352" t="n">
+        <v>3</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20240128</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>352</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>C123</t>
+        </is>
+      </c>
+      <c r="I353">
+        <f>C121-C122</f>
+        <v/>
+      </c>
+      <c r="J353" t="n">
+        <v>0.05792022604856684</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20240128,net_operating_expense_burden_change__20240128</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>144</v>
+      </c>
+      <c r="R353" t="n">
+        <v>1</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20250202</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>353</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I354">
+        <f>D121-D122</f>
+        <v/>
+      </c>
+      <c r="J354" t="n">
+        <v>0.01494307232648473</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20250202,net_operating_expense_burden_change__20250202</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>144</v>
+      </c>
+      <c r="R354" t="n">
+        <v>2</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20260201</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>354</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>E123</t>
+        </is>
+      </c>
+      <c r="I355">
+        <f>E121-E122</f>
+        <v/>
+      </c>
+      <c r="J355" t="n">
+        <v>-0.0375437372557203</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20260201,net_operating_expense_burden_change__20260201</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>144</v>
+      </c>
+      <c r="R355" t="n">
+        <v>3</v>
+      </c>
+      <c r="S355" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -35138,7 +37064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -37176,304 +39102,507 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>REPORTED MARGIN BRIDGE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Revenue (reported)</t>
         </is>
       </c>
       <c r="B115" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Income Statement'!B19</f>
         <v/>
       </c>
       <c r="C115" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Income Statement'!C19</f>
         <v/>
       </c>
       <c r="D115" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Income Statement'!D19</f>
         <v/>
       </c>
       <c r="E115" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Income Statement'!E19</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C116" s="15">
-        <f>C115-B115</f>
-        <v/>
-      </c>
-      <c r="D116" s="15">
-        <f>D115-C115</f>
-        <v/>
-      </c>
-      <c r="E116" s="15">
-        <f>E115-D115</f>
+          <t>Gross profit (reported)</t>
+        </is>
+      </c>
+      <c r="B116" s="12">
+        <f>'Income Statement'!B14</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>'Income Statement'!C14</f>
+        <v/>
+      </c>
+      <c r="D116" s="12">
+        <f>'Income Statement'!D14</f>
+        <v/>
+      </c>
+      <c r="E116" s="12">
+        <f>'Income Statement'!E14</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C117" s="14">
-        <f>IF(B115=0,NA(),C115/B115-1)</f>
-        <v/>
-      </c>
-      <c r="D117" s="14">
-        <f>IF(C115=0,NA(),D115/C115-1)</f>
-        <v/>
-      </c>
-      <c r="E117" s="14">
-        <f>IF(D115=0,NA(),E115/D115-1)</f>
+          <t>Operating profit (reported)</t>
+        </is>
+      </c>
+      <c r="B117" s="12">
+        <f>'Income Statement'!B16</f>
+        <v/>
+      </c>
+      <c r="C117" s="12">
+        <f>'Income Statement'!C16</f>
+        <v/>
+      </c>
+      <c r="D117" s="12">
+        <f>'Income Statement'!D16</f>
+        <v/>
+      </c>
+      <c r="E117" s="12">
+        <f>'Income Statement'!E16</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C118" s="15">
-        <f>(B115+C115)/2</f>
-        <v/>
-      </c>
-      <c r="D118" s="15">
-        <f>(C115+D115)/2</f>
-        <v/>
-      </c>
-      <c r="E118" s="15">
-        <f>(D115+E115)/2</f>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B118" s="14">
+        <f>IF(B115=0,NA(),B116/B115)</f>
+        <v/>
+      </c>
+      <c r="C118" s="14">
+        <f>IF(C115=0,NA(),C116/C115)</f>
+        <v/>
+      </c>
+      <c r="D118" s="14">
+        <f>IF(D115=0,NA(),D116/D115)</f>
+        <v/>
+      </c>
+      <c r="E118" s="14">
+        <f>IF(E115=0,NA(),E116/E115)</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="B119" s="14">
+        <f>IF(B115=0,NA(),B117/B115)</f>
+        <v/>
       </c>
       <c r="C119" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C118/'Condensed Financials'!C34)</f>
+        <f>IF(C115=0,NA(),C117/C115)</f>
         <v/>
       </c>
       <c r="D119" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D118/'Condensed Financials'!D34)</f>
+        <f>IF(D115=0,NA(),D117/D115)</f>
         <v/>
       </c>
       <c r="E119" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E118/'Condensed Financials'!E34)</f>
+        <f>IF(E115=0,NA(),E117/E115)</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B120" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C120" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D120" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E120" s="12">
-        <f>'Balance Sheet'!E23</f>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="B120" s="14">
+        <f>IF(B115=0,NA(),(B116-B117)/B115)</f>
+        <v/>
+      </c>
+      <c r="C120" s="14">
+        <f>IF(C115=0,NA(),(C116-C117)/C115)</f>
+        <v/>
+      </c>
+      <c r="D120" s="14">
+        <f>IF(D115=0,NA(),(D116-D117)/D115)</f>
+        <v/>
+      </c>
+      <c r="E120" s="14">
+        <f>IF(E115=0,NA(),(E116-E117)/E115)</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C121" s="15">
-        <f>C120-B120</f>
-        <v/>
-      </c>
-      <c r="D121" s="15">
-        <f>D120-C120</f>
-        <v/>
-      </c>
-      <c r="E121" s="15">
-        <f>E120-D120</f>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C121" s="14">
+        <f>C118-B118</f>
+        <v/>
+      </c>
+      <c r="D121" s="14">
+        <f>D118-C118</f>
+        <v/>
+      </c>
+      <c r="E121" s="14">
+        <f>E118-D118</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Change in net operating expense burden</t>
         </is>
       </c>
       <c r="C122" s="14">
-        <f>IF(B120=0,NA(),C120/B120-1)</f>
+        <f>C120-B120</f>
         <v/>
       </c>
       <c r="D122" s="14">
-        <f>IF(C120=0,NA(),D120/C120-1)</f>
+        <f>D120-C120</f>
         <v/>
       </c>
       <c r="E122" s="14">
-        <f>IF(D120=0,NA(),E120/D120-1)</f>
+        <f>E120-D120</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C123" s="15">
-        <f>(B120+C120)/2</f>
-        <v/>
-      </c>
-      <c r="D123" s="15">
-        <f>(C120+D120)/2</f>
-        <v/>
-      </c>
-      <c r="E123" s="15">
-        <f>(D120+E120)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C124" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C123/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D124" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D123/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E124" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E123/'Condensed Financials'!E34)</f>
-        <v/>
-      </c>
-    </row>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C123" s="14">
+        <f>C121-C122</f>
+        <v/>
+      </c>
+      <c r="D123" s="14">
+        <f>D121-D122</f>
+        <v/>
+      </c>
+      <c r="E123" s="14">
+        <f>E121-E122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B125" s="12">
-        <f>B115+B120</f>
-        <v/>
-      </c>
-      <c r="C125" s="12">
-        <f>C115+C120</f>
-        <v/>
-      </c>
-      <c r="D125" s="12">
-        <f>D115+D120</f>
-        <v/>
-      </c>
-      <c r="E125" s="12">
-        <f>E115+E120</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C126" s="15">
-        <f>C125-B125</f>
-        <v/>
-      </c>
-      <c r="D126" s="15">
-        <f>D125-C125</f>
-        <v/>
-      </c>
-      <c r="E126" s="15">
-        <f>E125-D125</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B126" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C126" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D126" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E126" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C127" s="14">
-        <f>IF(B125=0,NA(),C125/B125-1)</f>
-        <v/>
-      </c>
-      <c r="D127" s="14">
-        <f>IF(C125=0,NA(),D125/C125-1)</f>
-        <v/>
-      </c>
-      <c r="E127" s="14">
-        <f>IF(D125=0,NA(),E125/D125-1)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C127" s="15">
+        <f>C126-B126</f>
+        <v/>
+      </c>
+      <c r="D127" s="15">
+        <f>D126-C126</f>
+        <v/>
+      </c>
+      <c r="E127" s="15">
+        <f>E126-D126</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C128" s="15">
-        <f>(B125+C125)/2</f>
-        <v/>
-      </c>
-      <c r="D128" s="15">
-        <f>(C125+D125)/2</f>
-        <v/>
-      </c>
-      <c r="E128" s="15">
-        <f>(D125+E125)/2</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C128" s="14">
+        <f>IF(B126=0,NA(),C126/B126-1)</f>
+        <v/>
+      </c>
+      <c r="D128" s="14">
+        <f>IF(C126=0,NA(),D126/C126-1)</f>
+        <v/>
+      </c>
+      <c r="E128" s="14">
+        <f>IF(D126=0,NA(),E126/D126-1)</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C129" s="15">
+        <f>(B126+C126)/2</f>
+        <v/>
+      </c>
+      <c r="D129" s="15">
+        <f>(C126+D126)/2</f>
+        <v/>
+      </c>
+      <c r="E129" s="15">
+        <f>(D126+E126)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C130" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C129/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D130" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D129/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E130" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E129/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B131" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C131" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D131" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E131" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C132" s="15">
+        <f>C131-B131</f>
+        <v/>
+      </c>
+      <c r="D132" s="15">
+        <f>D131-C131</f>
+        <v/>
+      </c>
+      <c r="E132" s="15">
+        <f>E131-D131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C133" s="14">
+        <f>IF(B131=0,NA(),C131/B131-1)</f>
+        <v/>
+      </c>
+      <c r="D133" s="14">
+        <f>IF(C131=0,NA(),D131/C131-1)</f>
+        <v/>
+      </c>
+      <c r="E133" s="14">
+        <f>IF(D131=0,NA(),E131/D131-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C134" s="15">
+        <f>(B131+C131)/2</f>
+        <v/>
+      </c>
+      <c r="D134" s="15">
+        <f>(C131+D131)/2</f>
+        <v/>
+      </c>
+      <c r="E134" s="15">
+        <f>(D131+E131)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C135" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C134/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D135" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D134/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E135" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E134/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B136" s="12">
+        <f>B126+B131</f>
+        <v/>
+      </c>
+      <c r="C136" s="12">
+        <f>C126+C131</f>
+        <v/>
+      </c>
+      <c r="D136" s="12">
+        <f>D126+D131</f>
+        <v/>
+      </c>
+      <c r="E136" s="12">
+        <f>E126+E131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C137" s="15">
+        <f>C136-B136</f>
+        <v/>
+      </c>
+      <c r="D137" s="15">
+        <f>D136-C136</f>
+        <v/>
+      </c>
+      <c r="E137" s="15">
+        <f>E136-D136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C138" s="14">
+        <f>IF(B136=0,NA(),C136/B136-1)</f>
+        <v/>
+      </c>
+      <c r="D138" s="14">
+        <f>IF(C136=0,NA(),D136/C136-1)</f>
+        <v/>
+      </c>
+      <c r="E138" s="14">
+        <f>IF(D136=0,NA(),E136/D136-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C139" s="15">
+        <f>(B136+C136)/2</f>
+        <v/>
+      </c>
+      <c r="D139" s="15">
+        <f>(C136+D136)/2</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>(D136+E136)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C129" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C128/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D129" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D128/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E129" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E128/'Condensed Financials'!E34)</f>
+      <c r="C140" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C139/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D140" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D139/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E140" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E139/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -1301,182 +1301,262 @@
         <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C128" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D128" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E128" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C129" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="D129" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="E129" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="D130" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="E130" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="C131" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="D131" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="E131" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="C132" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="D132" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="E132" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="C136" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D127" authorId="0" shapeId="0">
+    <comment ref="D136" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E127" authorId="0" shapeId="0">
+    <comment ref="E136" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D128" authorId="0" shapeId="0">
+    <comment ref="D137" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E128" authorId="0" shapeId="0">
+    <comment ref="E137" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0">
+    <comment ref="C138" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D129" authorId="0" shapeId="0">
+    <comment ref="D138" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E129" authorId="0" shapeId="0">
+    <comment ref="E138" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C139" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D130" authorId="0" shapeId="0">
+    <comment ref="D139" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E130" authorId="0" shapeId="0">
+    <comment ref="E139" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C141" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0">
+    <comment ref="D141" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E132" authorId="0" shapeId="0">
+    <comment ref="E141" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C133" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D133" authorId="0" shapeId="0">
+    <comment ref="D142" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E133" authorId="0" shapeId="0">
+    <comment ref="E142" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C134" authorId="0" shapeId="0">
+    <comment ref="C143" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D134" authorId="0" shapeId="0">
+    <comment ref="D143" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E134" authorId="0" shapeId="0">
+    <comment ref="E143" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C135" authorId="0" shapeId="0">
+    <comment ref="C144" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D135" authorId="0" shapeId="0">
+    <comment ref="D144" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E135" authorId="0" shapeId="0">
+    <comment ref="E144" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C146" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D137" authorId="0" shapeId="0">
+    <comment ref="D146" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E137" authorId="0" shapeId="0">
+    <comment ref="E146" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C138" authorId="0" shapeId="0">
+    <comment ref="C147" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0">
+    <comment ref="D147" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E138" authorId="0" shapeId="0">
+    <comment ref="E147" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C139" authorId="0" shapeId="0">
+    <comment ref="C148" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D139" authorId="0" shapeId="0">
+    <comment ref="D148" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E139" authorId="0" shapeId="0">
+    <comment ref="E148" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C140" authorId="0" shapeId="0">
+    <comment ref="C149" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0">
+    <comment ref="D149" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E140" authorId="0" shapeId="0">
+    <comment ref="E149" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -2299,7 +2379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4178,7 +4258,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C127:E127</t>
+          <t>C136:E136</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4208,7 +4288,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C128:E128</t>
+          <t>C137:E137</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -4238,7 +4318,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C129:E129</t>
+          <t>C138:E138</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4268,7 +4348,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C130:E130</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4298,7 +4378,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C132:E132</t>
+          <t>C141:E141</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4328,7 +4408,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C133:E133</t>
+          <t>C142:E142</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4358,7 +4438,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C134:E134</t>
+          <t>C143:E143</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4388,7 +4468,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C135:E135</t>
+          <t>C144:E144</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4418,7 +4498,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C137:E137</t>
+          <t>C146:E146</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4448,7 +4528,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C138:E138</t>
+          <t>C147:E147</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4478,7 +4558,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C139:E139</t>
+          <t>C148:E148</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4508,7 +4588,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C140:E140</t>
+          <t>C149:E149</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -5444,6 +5524,156 @@
       <c r="F107" s="10" t="inlineStr">
         <is>
           <t>gross_margin_change, net_operating_expense_burden_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>B128:E128</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>C129:E129</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>C130:E130</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>C131:E131</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>C132:E132</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
         </is>
       </c>
     </row>
@@ -5901,7 +6131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S355"/>
+  <dimension ref="A1:S371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23153,11 +23383,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C127</t>
+          <t>C136</t>
         </is>
       </c>
       <c r="I218">
-        <f>C126-B126</f>
+        <f>C135-B135</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -23229,11 +23459,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D136</t>
         </is>
       </c>
       <c r="I219">
-        <f>D126-C126</f>
+        <f>D135-C135</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -23305,11 +23535,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E127</t>
+          <t>E136</t>
         </is>
       </c>
       <c r="I220">
-        <f>E126-D126</f>
+        <f>E135-D135</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -23381,11 +23611,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C128</t>
+          <t>C137</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B126=0,NA(),C126/B126-1)</f>
+        <f>IF(B135=0,NA(),C135/B135-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -23462,11 +23692,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D137</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C126=0,NA(),D126/C126-1)</f>
+        <f>IF(C135=0,NA(),D135/C135-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -23543,11 +23773,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E128</t>
+          <t>E137</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D126=0,NA(),E126/D126-1)</f>
+        <f>IF(D135=0,NA(),E135/D135-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -23624,11 +23854,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C129</t>
+          <t>C138</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B126+C126)/2</f>
+        <f>(B135+C135)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -23700,11 +23930,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D129</t>
+          <t>D138</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C126+D126)/2</f>
+        <f>(C135+D135)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -23776,11 +24006,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E129</t>
+          <t>E138</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D126+E126)/2</f>
+        <f>(D135+E135)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -23852,11 +24082,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C130</t>
+          <t>C139</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C129/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C138/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -23933,11 +24163,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D130</t>
+          <t>D139</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D129/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D138/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -24014,11 +24244,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E130</t>
+          <t>E139</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E129/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E138/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -24095,11 +24325,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C132</t>
+          <t>C141</t>
         </is>
       </c>
       <c r="I230">
-        <f>C131-B131</f>
+        <f>C140-B140</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -24171,11 +24401,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D132</t>
+          <t>D141</t>
         </is>
       </c>
       <c r="I231">
-        <f>D131-C131</f>
+        <f>D140-C140</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -24247,11 +24477,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E132</t>
+          <t>E141</t>
         </is>
       </c>
       <c r="I232">
-        <f>E131-D131</f>
+        <f>E140-D140</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -24323,11 +24553,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C133</t>
+          <t>C142</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B131=0,NA(),C131/B131-1)</f>
+        <f>IF(B140=0,NA(),C140/B140-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -24404,11 +24634,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D133</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C131=0,NA(),D131/C131-1)</f>
+        <f>IF(C140=0,NA(),D140/C140-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -24485,11 +24715,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E133</t>
+          <t>E142</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D131=0,NA(),E131/D131-1)</f>
+        <f>IF(D140=0,NA(),E140/D140-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -24566,11 +24796,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C134</t>
+          <t>C143</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B131+C131)/2</f>
+        <f>(B140+C140)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -24642,11 +24872,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D134</t>
+          <t>D143</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C131+D131)/2</f>
+        <f>(C140+D140)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -24718,11 +24948,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E134</t>
+          <t>E143</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D131+E131)/2</f>
+        <f>(D140+E140)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -24794,11 +25024,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C135</t>
+          <t>C144</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C134/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C143/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -24875,11 +25105,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D135</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D134/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D143/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -24956,11 +25186,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E135</t>
+          <t>E144</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E134/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E143/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -25037,11 +25267,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C137</t>
+          <t>C146</t>
         </is>
       </c>
       <c r="I242">
-        <f>C136-B136</f>
+        <f>C145-B145</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -25113,11 +25343,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D137</t>
+          <t>D146</t>
         </is>
       </c>
       <c r="I243">
-        <f>D136-C136</f>
+        <f>D145-C145</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -25189,11 +25419,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E137</t>
+          <t>E146</t>
         </is>
       </c>
       <c r="I244">
-        <f>E136-D136</f>
+        <f>E145-D145</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -25265,11 +25495,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C138</t>
+          <t>C147</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B136=0,NA(),C136/B136-1)</f>
+        <f>IF(B145=0,NA(),C145/B145-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -25346,11 +25576,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D138</t>
+          <t>D147</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C136=0,NA(),D136/C136-1)</f>
+        <f>IF(C145=0,NA(),D145/C145-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -25427,11 +25657,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E138</t>
+          <t>E147</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D136=0,NA(),E136/D136-1)</f>
+        <f>IF(D145=0,NA(),E145/D145-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -25508,11 +25738,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C139</t>
+          <t>C148</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B136+C136)/2</f>
+        <f>(B145+C145)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -25584,11 +25814,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D139</t>
+          <t>D148</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C136+D136)/2</f>
+        <f>(C145+D145)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -25660,11 +25890,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E139</t>
+          <t>E148</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D136+E136)/2</f>
+        <f>(D145+E145)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -25736,11 +25966,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C140</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C139/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C148/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -25817,11 +26047,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D140</t>
+          <t>D149</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D139/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D148/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -25898,11 +26128,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E140</t>
+          <t>E149</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E139/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E148/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -33980,6 +34210,1267 @@
         <v>3</v>
       </c>
       <c r="S355" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20230129</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>355</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2023-01-29</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>B128</t>
+        </is>
+      </c>
+      <c r="I356">
+        <f>IF(B127=0,NA(),B126/B127)</f>
+        <v/>
+      </c>
+      <c r="J356" t="n">
+        <v>0.1784555561062807</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>145</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240128</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>356</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>C128</t>
+        </is>
+      </c>
+      <c r="I357">
+        <f>IF(C127=0,NA(),C126/C127)</f>
+        <v/>
+      </c>
+      <c r="J357" t="n">
+        <v>0.1375988925572169</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>145</v>
+      </c>
+      <c r="R357" t="n">
+        <v>1</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20250202</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>357</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I358">
+        <f>IF(D127=0,NA(),D126/D127)</f>
+        <v/>
+      </c>
+      <c r="J358" t="n">
+        <v>0.1361979447543409</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>145</v>
+      </c>
+      <c r="R358" t="n">
+        <v>2</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20260201</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>358</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>E128</t>
+        </is>
+      </c>
+      <c r="I359">
+        <f>IF(E127=0,NA(),E126/E127)</f>
+        <v/>
+      </c>
+      <c r="J359" t="n">
+        <v>0.1531851097941023</v>
+      </c>
+      <c r="K359" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>145</v>
+      </c>
+      <c r="R359" t="n">
+        <v>3</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>inventory_change__20240128</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>359</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>C129</t>
+        </is>
+      </c>
+      <c r="I360">
+        <f>C126-B126</f>
+        <v/>
+      </c>
+      <c r="J360" t="n">
+        <v>-123765</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>146</v>
+      </c>
+      <c r="R360" t="n">
+        <v>1</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>inventory_change__20250202</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>360</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D129</t>
+        </is>
+      </c>
+      <c r="I361">
+        <f>D126-C126</f>
+        <v/>
+      </c>
+      <c r="J361" t="n">
+        <v>118479</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>146</v>
+      </c>
+      <c r="R361" t="n">
+        <v>2</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>inventory_change__20260201</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>361</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>E129</t>
+        </is>
+      </c>
+      <c r="I362">
+        <f>E126-D126</f>
+        <v/>
+      </c>
+      <c r="J362" t="n">
+        <v>258672</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>146</v>
+      </c>
+      <c r="R362" t="n">
+        <v>3</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20240128</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>362</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>C130</t>
+        </is>
+      </c>
+      <c r="I363">
+        <f>B128*(C127-B127)</f>
+        <v/>
+      </c>
+      <c r="J363" t="n">
+        <v>269246.6048309121</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20230129</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>147</v>
+      </c>
+      <c r="R363" t="n">
+        <v>1</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20250202</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>363</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D130</t>
+        </is>
+      </c>
+      <c r="I364">
+        <f>C128*(D127-C127)</f>
+        <v/>
+      </c>
+      <c r="J364" t="n">
+        <v>133312.4118562745</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240128</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q364" t="n">
+        <v>147</v>
+      </c>
+      <c r="R364" t="n">
+        <v>2</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20260201</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>364</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>E130</t>
+        </is>
+      </c>
+      <c r="I365">
+        <f>D128*(E127-D127)</f>
+        <v/>
+      </c>
+      <c r="J365" t="n">
+        <v>70070.30142954475</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20250202</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q365" t="n">
+        <v>147</v>
+      </c>
+      <c r="R365" t="n">
+        <v>3</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20240128</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>365</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>C131</t>
+        </is>
+      </c>
+      <c r="I366">
+        <f>C127*(C128-B128)</f>
+        <v/>
+      </c>
+      <c r="J366" t="n">
+        <v>-393011.604830912</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240128,inventory_intensity__20230129</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>148</v>
+      </c>
+      <c r="R366" t="n">
+        <v>1</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20250202</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>366</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>D131</t>
+        </is>
+      </c>
+      <c r="I367">
+        <f>D127*(D128-C128)</f>
+        <v/>
+      </c>
+      <c r="J367" t="n">
+        <v>-14833.41185627456</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20250202,inventory_intensity__20240128</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>148</v>
+      </c>
+      <c r="R367" t="n">
+        <v>2</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20260201</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>367</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>E131</t>
+        </is>
+      </c>
+      <c r="I368">
+        <f>E127*(E128-D128)</f>
+        <v/>
+      </c>
+      <c r="J368" t="n">
+        <v>188601.6985704551</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20260201,inventory_intensity__20250202</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>148</v>
+      </c>
+      <c r="R368" t="n">
+        <v>3</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20240128</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>368</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>C132</t>
+        </is>
+      </c>
+      <c r="I369">
+        <f>C130+C131</f>
+        <v/>
+      </c>
+      <c r="J369" t="n">
+        <v>-123764.9999999998</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20240128,inventory_intensity_effect__20240128</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>149</v>
+      </c>
+      <c r="R369" t="n">
+        <v>1</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20250202</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>369</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I370">
+        <f>D130+D131</f>
+        <v/>
+      </c>
+      <c r="J370" t="n">
+        <v>118478.9999999999</v>
+      </c>
+      <c r="K370" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20250202,inventory_intensity_effect__20250202</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>149</v>
+      </c>
+      <c r="R370" t="n">
+        <v>2</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20260201</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>370</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>E132</t>
+        </is>
+      </c>
+      <c r="I371">
+        <f>E130+E131</f>
+        <v/>
+      </c>
+      <c r="J371" t="n">
+        <v>258671.9999999998</v>
+      </c>
+      <c r="K371" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20260201,inventory_intensity_effect__20260201</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>149</v>
+      </c>
+      <c r="R371" t="n">
+        <v>3</v>
+      </c>
+      <c r="S371" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -37064,7 +38555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -39305,304 +40796,457 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>INVENTORY GROWTH AND INTENSITY CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Inventory (reported)</t>
         </is>
       </c>
       <c r="B126" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Balance Sheet'!B9</f>
         <v/>
       </c>
       <c r="C126" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Balance Sheet'!C9</f>
         <v/>
       </c>
       <c r="D126" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Balance Sheet'!D9</f>
         <v/>
       </c>
       <c r="E126" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Balance Sheet'!E9</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C127" s="15">
-        <f>C126-B126</f>
-        <v/>
-      </c>
-      <c r="D127" s="15">
-        <f>D126-C126</f>
-        <v/>
-      </c>
-      <c r="E127" s="15">
-        <f>E126-D126</f>
+          <t>Revenue (reported)</t>
+        </is>
+      </c>
+      <c r="B127" s="12">
+        <f>'Income Statement'!B19</f>
+        <v/>
+      </c>
+      <c r="C127" s="12">
+        <f>'Income Statement'!C19</f>
+        <v/>
+      </c>
+      <c r="D127" s="12">
+        <f>'Income Statement'!D19</f>
+        <v/>
+      </c>
+      <c r="E127" s="12">
+        <f>'Income Statement'!E19</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="B128" s="14">
+        <f>IF(B127=0,NA(),B126/B127)</f>
+        <v/>
       </c>
       <c r="C128" s="14">
-        <f>IF(B126=0,NA(),C126/B126-1)</f>
+        <f>IF(C127=0,NA(),C126/C127)</f>
         <v/>
       </c>
       <c r="D128" s="14">
-        <f>IF(C126=0,NA(),D126/C126-1)</f>
+        <f>IF(D127=0,NA(),D126/D127)</f>
         <v/>
       </c>
       <c r="E128" s="14">
-        <f>IF(D126=0,NA(),E126/D126-1)</f>
+        <f>IF(E127=0,NA(),E126/E127)</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
+          <t>Change in inventory</t>
         </is>
       </c>
       <c r="C129" s="15">
-        <f>(B126+C126)/2</f>
+        <f>C126-B126</f>
         <v/>
       </c>
       <c r="D129" s="15">
-        <f>(C126+D126)/2</f>
+        <f>D126-C126</f>
         <v/>
       </c>
       <c r="E129" s="15">
-        <f>(D126+E126)/2</f>
+        <f>E126-D126</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C130" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C129/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D130" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D129/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E130" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E129/'Condensed Financials'!E34)</f>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C130" s="15">
+        <f>B128*(C127-B127)</f>
+        <v/>
+      </c>
+      <c r="D130" s="15">
+        <f>C128*(D127-C127)</f>
+        <v/>
+      </c>
+      <c r="E130" s="15">
+        <f>D128*(E127-D127)</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B131" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C131" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D131" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E131" s="12">
-        <f>'Balance Sheet'!E23</f>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C131" s="15">
+        <f>C127*(C128-B128)</f>
+        <v/>
+      </c>
+      <c r="D131" s="15">
+        <f>D127*(D128-C128)</f>
+        <v/>
+      </c>
+      <c r="E131" s="15">
+        <f>E127*(E128-D128)</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Reconstructed change in inventory</t>
         </is>
       </c>
       <c r="C132" s="15">
-        <f>C131-B131</f>
+        <f>C130+C131</f>
         <v/>
       </c>
       <c r="D132" s="15">
-        <f>D131-C131</f>
+        <f>D130+D131</f>
         <v/>
       </c>
       <c r="E132" s="15">
-        <f>E131-D131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C133" s="14">
-        <f>IF(B131=0,NA(),C131/B131-1)</f>
-        <v/>
-      </c>
-      <c r="D133" s="14">
-        <f>IF(C131=0,NA(),D131/C131-1)</f>
-        <v/>
-      </c>
-      <c r="E133" s="14">
-        <f>IF(D131=0,NA(),E131/D131-1)</f>
-        <v/>
-      </c>
-    </row>
+        <f>E130+E131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133"/>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C134" s="15">
-        <f>(B131+C131)/2</f>
-        <v/>
-      </c>
-      <c r="D134" s="15">
-        <f>(C131+D131)/2</f>
-        <v/>
-      </c>
-      <c r="E134" s="15">
-        <f>(D131+E131)/2</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C135" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C134/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D135" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D134/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E135" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E134/'Condensed Financials'!E34)</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B135" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C135" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D135" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E135" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B136" s="12">
-        <f>B126+B131</f>
-        <v/>
-      </c>
-      <c r="C136" s="12">
-        <f>C126+C131</f>
-        <v/>
-      </c>
-      <c r="D136" s="12">
-        <f>D126+D131</f>
-        <v/>
-      </c>
-      <c r="E136" s="12">
-        <f>E126+E131</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C136" s="15">
+        <f>C135-B135</f>
+        <v/>
+      </c>
+      <c r="D136" s="15">
+        <f>D135-C135</f>
+        <v/>
+      </c>
+      <c r="E136" s="15">
+        <f>E135-D135</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C137" s="15">
-        <f>C136-B136</f>
-        <v/>
-      </c>
-      <c r="D137" s="15">
-        <f>D136-C136</f>
-        <v/>
-      </c>
-      <c r="E137" s="15">
-        <f>E136-D136</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C137" s="14">
+        <f>IF(B135=0,NA(),C135/B135-1)</f>
+        <v/>
+      </c>
+      <c r="D137" s="14">
+        <f>IF(C135=0,NA(),D135/C135-1)</f>
+        <v/>
+      </c>
+      <c r="E137" s="14">
+        <f>IF(D135=0,NA(),E135/D135-1)</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C138" s="14">
-        <f>IF(B136=0,NA(),C136/B136-1)</f>
-        <v/>
-      </c>
-      <c r="D138" s="14">
-        <f>IF(C136=0,NA(),D136/C136-1)</f>
-        <v/>
-      </c>
-      <c r="E138" s="14">
-        <f>IF(D136=0,NA(),E136/D136-1)</f>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C138" s="15">
+        <f>(B135+C135)/2</f>
+        <v/>
+      </c>
+      <c r="D138" s="15">
+        <f>(C135+D135)/2</f>
+        <v/>
+      </c>
+      <c r="E138" s="15">
+        <f>(D135+E135)/2</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C139" s="15">
-        <f>(B136+C136)/2</f>
-        <v/>
-      </c>
-      <c r="D139" s="15">
-        <f>(C136+D136)/2</f>
-        <v/>
-      </c>
-      <c r="E139" s="15">
-        <f>(D136+E136)/2</f>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C139" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C138/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D139" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D138/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E139" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E138/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B140" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C140" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D140" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E140" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C141" s="15">
+        <f>C140-B140</f>
+        <v/>
+      </c>
+      <c r="D141" s="15">
+        <f>D140-C140</f>
+        <v/>
+      </c>
+      <c r="E141" s="15">
+        <f>E140-D140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C142" s="14">
+        <f>IF(B140=0,NA(),C140/B140-1)</f>
+        <v/>
+      </c>
+      <c r="D142" s="14">
+        <f>IF(C140=0,NA(),D140/C140-1)</f>
+        <v/>
+      </c>
+      <c r="E142" s="14">
+        <f>IF(D140=0,NA(),E140/D140-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C143" s="15">
+        <f>(B140+C140)/2</f>
+        <v/>
+      </c>
+      <c r="D143" s="15">
+        <f>(C140+D140)/2</f>
+        <v/>
+      </c>
+      <c r="E143" s="15">
+        <f>(D140+E140)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C144" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C143/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D144" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D143/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E144" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E143/'Condensed Financials'!E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B145" s="12">
+        <f>B135+B140</f>
+        <v/>
+      </c>
+      <c r="C145" s="12">
+        <f>C135+C140</f>
+        <v/>
+      </c>
+      <c r="D145" s="12">
+        <f>D135+D140</f>
+        <v/>
+      </c>
+      <c r="E145" s="12">
+        <f>E135+E140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C146" s="15">
+        <f>C145-B145</f>
+        <v/>
+      </c>
+      <c r="D146" s="15">
+        <f>D145-C145</f>
+        <v/>
+      </c>
+      <c r="E146" s="15">
+        <f>E145-D145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C147" s="14">
+        <f>IF(B145=0,NA(),C145/B145-1)</f>
+        <v/>
+      </c>
+      <c r="D147" s="14">
+        <f>IF(C145=0,NA(),D145/C145-1)</f>
+        <v/>
+      </c>
+      <c r="E147" s="14">
+        <f>IF(D145=0,NA(),E145/D145-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C148" s="15">
+        <f>(B145+C145)/2</f>
+        <v/>
+      </c>
+      <c r="D148" s="15">
+        <f>(C145+D145)/2</f>
+        <v/>
+      </c>
+      <c r="E148" s="15">
+        <f>(D145+E145)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C140" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C139/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D140" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D139/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E140" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E139/'Condensed Financials'!E34)</f>
+      <c r="C149" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C148/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D149" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D148/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E149" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E148/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>

--- a/release/lululemon/Lululemon_Answer_Key.xlsx
+++ b/release/lululemon/Lululemon_Answer_Key.xlsx
@@ -1381,182 +1381,212 @@
         <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
       </text>
     </comment>
-    <comment ref="C136" authorId="0" shapeId="0">
+    <comment ref="C134" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="D134" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="E134" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="C135" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="D135" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="E135" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="C139" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0">
+    <comment ref="D139" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E136" authorId="0" shapeId="0">
+    <comment ref="E139" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C140" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D137" authorId="0" shapeId="0">
+    <comment ref="D140" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E137" authorId="0" shapeId="0">
+    <comment ref="E140" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C138" authorId="0" shapeId="0">
+    <comment ref="C141" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0">
+    <comment ref="D141" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E138" authorId="0" shapeId="0">
+    <comment ref="E141" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C139" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D139" authorId="0" shapeId="0">
+    <comment ref="D142" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E139" authorId="0" shapeId="0">
+    <comment ref="E142" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C141" authorId="0" shapeId="0">
+    <comment ref="C144" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D141" authorId="0" shapeId="0">
+    <comment ref="D144" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E141" authorId="0" shapeId="0">
+    <comment ref="E144" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0">
+    <comment ref="C145" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D142" authorId="0" shapeId="0">
+    <comment ref="D145" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E142" authorId="0" shapeId="0">
+    <comment ref="E145" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C143" authorId="0" shapeId="0">
+    <comment ref="C146" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D143" authorId="0" shapeId="0">
+    <comment ref="D146" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E143" authorId="0" shapeId="0">
+    <comment ref="E146" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C144" authorId="0" shapeId="0">
+    <comment ref="C147" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D144" authorId="0" shapeId="0">
+    <comment ref="D147" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E144" authorId="0" shapeId="0">
+    <comment ref="E147" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C146" authorId="0" shapeId="0">
+    <comment ref="C149" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D146" authorId="0" shapeId="0">
+    <comment ref="D149" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E146" authorId="0" shapeId="0">
+    <comment ref="E149" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C147" authorId="0" shapeId="0">
+    <comment ref="C150" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D147" authorId="0" shapeId="0">
+    <comment ref="D150" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E147" authorId="0" shapeId="0">
+    <comment ref="E150" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C148" authorId="0" shapeId="0">
+    <comment ref="C151" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D148" authorId="0" shapeId="0">
+    <comment ref="D151" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E148" authorId="0" shapeId="0">
+    <comment ref="E151" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C149" authorId="0" shapeId="0">
+    <comment ref="C152" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D149" authorId="0" shapeId="0">
+    <comment ref="D152" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E149" authorId="0" shapeId="0">
+    <comment ref="E152" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
@@ -2379,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4258,7 +4288,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C136:E136</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4288,7 +4318,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C137:E137</t>
+          <t>C140:E140</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -4318,7 +4348,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C138:E138</t>
+          <t>C141:E141</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4348,7 +4378,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C139:E139</t>
+          <t>C142:E142</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4378,7 +4408,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C141:E141</t>
+          <t>C144:E144</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4408,7 +4438,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C142:E142</t>
+          <t>C145:E145</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4438,7 +4468,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C143:E143</t>
+          <t>C146:E146</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4468,7 +4498,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C144:E144</t>
+          <t>C147:E147</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4498,7 +4528,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C146:E146</t>
+          <t>C149:E149</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4528,7 +4558,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C147:E147</t>
+          <t>C150:E150</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4558,7 +4588,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C148:E148</t>
+          <t>C151:E151</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4588,7 +4618,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C149:E149</t>
+          <t>C152:E152</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -5674,6 +5704,66 @@
       <c r="F112" s="10" t="inlineStr">
         <is>
           <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>C134:E134</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>C135:E135</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S371"/>
+  <dimension ref="A1:S377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23383,11 +23473,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C136</t>
+          <t>C139</t>
         </is>
       </c>
       <c r="I218">
-        <f>C135-B135</f>
+        <f>C138-B138</f>
         <v/>
       </c>
       <c r="J218" t="n">
@@ -23459,11 +23549,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D136</t>
+          <t>D139</t>
         </is>
       </c>
       <c r="I219">
-        <f>D135-C135</f>
+        <f>D138-C138</f>
         <v/>
       </c>
       <c r="J219" t="n">
@@ -23535,11 +23625,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>E136</t>
+          <t>E139</t>
         </is>
       </c>
       <c r="I220">
-        <f>E135-D135</f>
+        <f>E138-D138</f>
         <v/>
       </c>
       <c r="J220" t="n">
@@ -23611,11 +23701,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C137</t>
+          <t>C140</t>
         </is>
       </c>
       <c r="I221">
-        <f>IF(B135=0,NA(),C135/B135-1)</f>
+        <f>IF(B138=0,NA(),C138/B138-1)</f>
         <v/>
       </c>
       <c r="J221" t="n">
@@ -23692,11 +23782,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D137</t>
+          <t>D140</t>
         </is>
       </c>
       <c r="I222">
-        <f>IF(C135=0,NA(),D135/C135-1)</f>
+        <f>IF(C138=0,NA(),D138/C138-1)</f>
         <v/>
       </c>
       <c r="J222" t="n">
@@ -23773,11 +23863,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>E137</t>
+          <t>E140</t>
         </is>
       </c>
       <c r="I223">
-        <f>IF(D135=0,NA(),E135/D135-1)</f>
+        <f>IF(D138=0,NA(),E138/D138-1)</f>
         <v/>
       </c>
       <c r="J223" t="n">
@@ -23854,11 +23944,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C138</t>
+          <t>C141</t>
         </is>
       </c>
       <c r="I224">
-        <f>(B135+C135)/2</f>
+        <f>(B138+C138)/2</f>
         <v/>
       </c>
       <c r="J224" t="n">
@@ -23930,11 +24020,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D138</t>
+          <t>D141</t>
         </is>
       </c>
       <c r="I225">
-        <f>(C135+D135)/2</f>
+        <f>(C138+D138)/2</f>
         <v/>
       </c>
       <c r="J225" t="n">
@@ -24006,11 +24096,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>E138</t>
+          <t>E141</t>
         </is>
       </c>
       <c r="I226">
-        <f>(D135+E135)/2</f>
+        <f>(D138+E138)/2</f>
         <v/>
       </c>
       <c r="J226" t="n">
@@ -24082,11 +24172,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C139</t>
+          <t>C142</t>
         </is>
       </c>
       <c r="I227">
-        <f>IF('Condensed Financials'!C34=0,NA(),C138/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C141/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J227" t="n">
@@ -24163,11 +24253,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D139</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I228">
-        <f>IF('Condensed Financials'!D34=0,NA(),D138/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D141/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J228" t="n">
@@ -24244,11 +24334,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>E139</t>
+          <t>E142</t>
         </is>
       </c>
       <c r="I229">
-        <f>IF('Condensed Financials'!E34=0,NA(),E138/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E141/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J229" t="n">
@@ -24325,11 +24415,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C141</t>
+          <t>C144</t>
         </is>
       </c>
       <c r="I230">
-        <f>C140-B140</f>
+        <f>C143-B143</f>
         <v/>
       </c>
       <c r="J230" t="n">
@@ -24401,11 +24491,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D141</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I231">
-        <f>D140-C140</f>
+        <f>D143-C143</f>
         <v/>
       </c>
       <c r="J231" t="n">
@@ -24477,11 +24567,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>E141</t>
+          <t>E144</t>
         </is>
       </c>
       <c r="I232">
-        <f>E140-D140</f>
+        <f>E143-D143</f>
         <v/>
       </c>
       <c r="J232" t="n">
@@ -24553,11 +24643,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C142</t>
+          <t>C145</t>
         </is>
       </c>
       <c r="I233">
-        <f>IF(B140=0,NA(),C140/B140-1)</f>
+        <f>IF(B143=0,NA(),C143/B143-1)</f>
         <v/>
       </c>
       <c r="J233" t="n">
@@ -24634,11 +24724,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D145</t>
         </is>
       </c>
       <c r="I234">
-        <f>IF(C140=0,NA(),D140/C140-1)</f>
+        <f>IF(C143=0,NA(),D143/C143-1)</f>
         <v/>
       </c>
       <c r="J234" t="e">
@@ -24715,11 +24805,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>E142</t>
+          <t>E145</t>
         </is>
       </c>
       <c r="I235">
-        <f>IF(D140=0,NA(),E140/D140-1)</f>
+        <f>IF(D143=0,NA(),E143/D143-1)</f>
         <v/>
       </c>
       <c r="J235" t="n">
@@ -24796,11 +24886,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C146</t>
         </is>
       </c>
       <c r="I236">
-        <f>(B140+C140)/2</f>
+        <f>(B143+C143)/2</f>
         <v/>
       </c>
       <c r="J236" t="n">
@@ -24872,11 +24962,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D143</t>
+          <t>D146</t>
         </is>
       </c>
       <c r="I237">
-        <f>(C140+D140)/2</f>
+        <f>(C143+D143)/2</f>
         <v/>
       </c>
       <c r="J237" t="n">
@@ -24948,11 +25038,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>E143</t>
+          <t>E146</t>
         </is>
       </c>
       <c r="I238">
-        <f>(D140+E140)/2</f>
+        <f>(D143+E143)/2</f>
         <v/>
       </c>
       <c r="J238" t="n">
@@ -25024,11 +25114,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C144</t>
+          <t>C147</t>
         </is>
       </c>
       <c r="I239">
-        <f>IF('Condensed Financials'!C34=0,NA(),C143/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C146/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J239" t="n">
@@ -25105,11 +25195,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D147</t>
         </is>
       </c>
       <c r="I240">
-        <f>IF('Condensed Financials'!D34=0,NA(),D143/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D146/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J240" t="n">
@@ -25186,11 +25276,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>E144</t>
+          <t>E147</t>
         </is>
       </c>
       <c r="I241">
-        <f>IF('Condensed Financials'!E34=0,NA(),E143/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E146/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J241" t="n">
@@ -25267,11 +25357,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C146</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="I242">
-        <f>C145-B145</f>
+        <f>C148-B148</f>
         <v/>
       </c>
       <c r="J242" t="n">
@@ -25343,11 +25433,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D146</t>
+          <t>D149</t>
         </is>
       </c>
       <c r="I243">
-        <f>D145-C145</f>
+        <f>D148-C148</f>
         <v/>
       </c>
       <c r="J243" t="n">
@@ -25419,11 +25509,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>E146</t>
+          <t>E149</t>
         </is>
       </c>
       <c r="I244">
-        <f>E145-D145</f>
+        <f>E148-D148</f>
         <v/>
       </c>
       <c r="J244" t="n">
@@ -25495,11 +25585,11 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C147</t>
+          <t>C150</t>
         </is>
       </c>
       <c r="I245">
-        <f>IF(B145=0,NA(),C145/B145-1)</f>
+        <f>IF(B148=0,NA(),C148/B148-1)</f>
         <v/>
       </c>
       <c r="J245" t="n">
@@ -25576,11 +25666,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D147</t>
+          <t>D150</t>
         </is>
       </c>
       <c r="I246">
-        <f>IF(C145=0,NA(),D145/C145-1)</f>
+        <f>IF(C148=0,NA(),D148/C148-1)</f>
         <v/>
       </c>
       <c r="J246" t="n">
@@ -25657,11 +25747,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>E147</t>
+          <t>E150</t>
         </is>
       </c>
       <c r="I247">
-        <f>IF(D145=0,NA(),E145/D145-1)</f>
+        <f>IF(D148=0,NA(),E148/D148-1)</f>
         <v/>
       </c>
       <c r="J247" t="n">
@@ -25738,11 +25828,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C148</t>
+          <t>C151</t>
         </is>
       </c>
       <c r="I248">
-        <f>(B145+C145)/2</f>
+        <f>(B148+C148)/2</f>
         <v/>
       </c>
       <c r="J248" t="n">
@@ -25814,11 +25904,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D148</t>
+          <t>D151</t>
         </is>
       </c>
       <c r="I249">
-        <f>(C145+D145)/2</f>
+        <f>(C148+D148)/2</f>
         <v/>
       </c>
       <c r="J249" t="n">
@@ -25890,11 +25980,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>E148</t>
+          <t>E151</t>
         </is>
       </c>
       <c r="I250">
-        <f>(D145+E145)/2</f>
+        <f>(D148+E148)/2</f>
         <v/>
       </c>
       <c r="J250" t="n">
@@ -25966,11 +26056,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C152</t>
         </is>
       </c>
       <c r="I251">
-        <f>IF('Condensed Financials'!C34=0,NA(),C148/'Condensed Financials'!C34)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C151/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="J251" t="n">
@@ -26047,11 +26137,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D149</t>
+          <t>D152</t>
         </is>
       </c>
       <c r="I252">
-        <f>IF('Condensed Financials'!D34=0,NA(),D148/'Condensed Financials'!D34)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D151/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="J252" t="n">
@@ -26128,11 +26218,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>E149</t>
+          <t>E152</t>
         </is>
       </c>
       <c r="I253">
-        <f>IF('Condensed Financials'!E34=0,NA(),E148/'Condensed Financials'!E34)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E151/'Condensed Financials'!E34)</f>
         <v/>
       </c>
       <c r="J253" t="n">
@@ -35471,6 +35561,492 @@
         <v>3</v>
       </c>
       <c r="S371" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20240128</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>371</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>C134</t>
+        </is>
+      </c>
+      <c r="I372">
+        <f>-C129</f>
+        <v/>
+      </c>
+      <c r="J372" t="n">
+        <v>123765</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>inventory_change__20240128</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>150</v>
+      </c>
+      <c r="R372" t="n">
+        <v>1</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20250202</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>372</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I373">
+        <f>-D129</f>
+        <v/>
+      </c>
+      <c r="J373" t="n">
+        <v>-118479</v>
+      </c>
+      <c r="K373" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>inventory_change__20250202</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>150</v>
+      </c>
+      <c r="R373" t="n">
+        <v>2</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20260201</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>373</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>E134</t>
+        </is>
+      </c>
+      <c r="I374">
+        <f>-E129</f>
+        <v/>
+      </c>
+      <c r="J374" t="n">
+        <v>-258672</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>inventory_change__20260201</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>150</v>
+      </c>
+      <c r="R374" t="n">
+        <v>3</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20240128</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>374</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2024-01-28</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>C135</t>
+        </is>
+      </c>
+      <c r="I375">
+        <f>C133-C134</f>
+        <v/>
+      </c>
+      <c r="J375" t="n">
+        <v>-57181</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20240128</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>151</v>
+      </c>
+      <c r="R375" t="n">
+        <v>1</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20250202</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>375</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2025-02-02</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I376">
+        <f>D133-D134</f>
+        <v/>
+      </c>
+      <c r="J376" t="n">
+        <v>-37606</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20250202</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>151</v>
+      </c>
+      <c r="R376" t="n">
+        <v>2</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20260201</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>376</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2026-02-01</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>E135</t>
+        </is>
+      </c>
+      <c r="I377">
+        <f>E133-E134</f>
+        <v/>
+      </c>
+      <c r="J377" t="n">
+        <v>69962</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20260201</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>151</v>
+      </c>
+      <c r="R377" t="n">
+        <v>3</v>
+      </c>
+      <c r="S377" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
@@ -38555,7 +39131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -40945,308 +41521,369 @@
         <v/>
       </c>
     </row>
-    <row r="133"/>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>Inventory CF adjustment (reported)</t>
+        </is>
+      </c>
+      <c r="B133" s="12">
+        <f>'Cash Flow Statement'!B25</f>
+        <v/>
+      </c>
+      <c r="C133" s="12">
+        <f>'Cash Flow Statement'!C25</f>
+        <v/>
+      </c>
+      <c r="D133" s="12">
+        <f>'Cash Flow Statement'!D25</f>
+        <v/>
+      </c>
+      <c r="E133" s="12">
+        <f>'Cash Flow Statement'!E25</f>
+        <v/>
+      </c>
+    </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C134" s="15">
+        <f>-C129</f>
+        <v/>
+      </c>
+      <c r="D134" s="15">
+        <f>-D129</f>
+        <v/>
+      </c>
+      <c r="E134" s="15">
+        <f>-E129</f>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B135" s="12">
-        <f>'Balance Sheet'!B22</f>
-        <v/>
-      </c>
-      <c r="C135" s="12">
-        <f>'Balance Sheet'!C22</f>
-        <v/>
-      </c>
-      <c r="D135" s="12">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
-      </c>
-      <c r="E135" s="12">
-        <f>'Balance Sheet'!E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C136" s="15">
-        <f>C135-B135</f>
-        <v/>
-      </c>
-      <c r="D136" s="15">
-        <f>D135-C135</f>
-        <v/>
-      </c>
-      <c r="E136" s="15">
-        <f>E135-D135</f>
-        <v/>
-      </c>
-    </row>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C135" s="15">
+        <f>C133-C134</f>
+        <v/>
+      </c>
+      <c r="D135" s="15">
+        <f>D133-D134</f>
+        <v/>
+      </c>
+      <c r="E135" s="15">
+        <f>E133-E134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C137" s="14">
-        <f>IF(B135=0,NA(),C135/B135-1)</f>
-        <v/>
-      </c>
-      <c r="D137" s="14">
-        <f>IF(C135=0,NA(),D135/C135-1)</f>
-        <v/>
-      </c>
-      <c r="E137" s="14">
-        <f>IF(D135=0,NA(),E135/D135-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C138" s="15">
-        <f>(B135+C135)/2</f>
-        <v/>
-      </c>
-      <c r="D138" s="15">
-        <f>(C135+D135)/2</f>
-        <v/>
-      </c>
-      <c r="E138" s="15">
-        <f>(D135+E135)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B138" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C138" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D138" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E138" s="12">
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C139" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C138/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D139" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D138/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E139" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E138/'Condensed Financials'!E34)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C139" s="15">
+        <f>C138-B138</f>
+        <v/>
+      </c>
+      <c r="D139" s="15">
+        <f>D138-C138</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>E138-D138</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B140" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C140" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D140" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E140" s="12">
-        <f>'Balance Sheet'!E23</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C140" s="14">
+        <f>IF(B138=0,NA(),C138/B138-1)</f>
+        <v/>
+      </c>
+      <c r="D140" s="14">
+        <f>IF(C138=0,NA(),D138/C138-1)</f>
+        <v/>
+      </c>
+      <c r="E140" s="14">
+        <f>IF(D138=0,NA(),E138/D138-1)</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C141" s="15">
-        <f>C140-B140</f>
+        <f>(B138+C138)/2</f>
         <v/>
       </c>
       <c r="D141" s="15">
-        <f>D140-C140</f>
+        <f>(C138+D138)/2</f>
         <v/>
       </c>
       <c r="E141" s="15">
-        <f>E140-D140</f>
+        <f>(D138+E138)/2</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C142" s="14">
-        <f>IF(B140=0,NA(),C140/B140-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C141/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D142" s="14">
-        <f>IF(C140=0,NA(),D140/C140-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D141/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E142" s="14">
-        <f>IF(D140=0,NA(),E140/D140-1)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E141/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C143" s="15">
-        <f>(B140+C140)/2</f>
-        <v/>
-      </c>
-      <c r="D143" s="15">
-        <f>(C140+D140)/2</f>
-        <v/>
-      </c>
-      <c r="E143" s="15">
-        <f>(D140+E140)/2</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B143" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C143" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D143" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E143" s="12">
+        <f>'Balance Sheet'!E23</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C144" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C143/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D144" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D143/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E144" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E143/'Condensed Financials'!E34)</f>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C144" s="15">
+        <f>C143-B143</f>
+        <v/>
+      </c>
+      <c r="D144" s="15">
+        <f>D143-C143</f>
+        <v/>
+      </c>
+      <c r="E144" s="15">
+        <f>E143-D143</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B145" s="12">
-        <f>B135+B140</f>
-        <v/>
-      </c>
-      <c r="C145" s="12">
-        <f>C135+C140</f>
-        <v/>
-      </c>
-      <c r="D145" s="12">
-        <f>D135+D140</f>
-        <v/>
-      </c>
-      <c r="E145" s="12">
-        <f>E135+E140</f>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C145" s="14">
+        <f>IF(B143=0,NA(),C143/B143-1)</f>
+        <v/>
+      </c>
+      <c r="D145" s="14">
+        <f>IF(C143=0,NA(),D143/C143-1)</f>
+        <v/>
+      </c>
+      <c r="E145" s="14">
+        <f>IF(D143=0,NA(),E143/D143-1)</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C146" s="15">
-        <f>C145-B145</f>
+        <f>(B143+C143)/2</f>
         <v/>
       </c>
       <c r="D146" s="15">
-        <f>D145-C145</f>
+        <f>(C143+D143)/2</f>
         <v/>
       </c>
       <c r="E146" s="15">
-        <f>E145-D145</f>
+        <f>(D143+E143)/2</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C147" s="14">
-        <f>IF(B145=0,NA(),C145/B145-1)</f>
+        <f>IF('Condensed Financials'!C34=0,NA(),C146/'Condensed Financials'!C34)</f>
         <v/>
       </c>
       <c r="D147" s="14">
-        <f>IF(C145=0,NA(),D145/C145-1)</f>
+        <f>IF('Condensed Financials'!D34=0,NA(),D146/'Condensed Financials'!D34)</f>
         <v/>
       </c>
       <c r="E147" s="14">
-        <f>IF(D145=0,NA(),E145/D145-1)</f>
+        <f>IF('Condensed Financials'!E34=0,NA(),E146/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C148" s="15">
-        <f>(B145+C145)/2</f>
-        <v/>
-      </c>
-      <c r="D148" s="15">
-        <f>(C145+D145)/2</f>
-        <v/>
-      </c>
-      <c r="E148" s="15">
-        <f>(D145+E145)/2</f>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B148" s="12">
+        <f>B138+B143</f>
+        <v/>
+      </c>
+      <c r="C148" s="12">
+        <f>C138+C143</f>
+        <v/>
+      </c>
+      <c r="D148" s="12">
+        <f>D138+D143</f>
+        <v/>
+      </c>
+      <c r="E148" s="12">
+        <f>E138+E143</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C149" s="15">
+        <f>C148-B148</f>
+        <v/>
+      </c>
+      <c r="D149" s="15">
+        <f>D148-C148</f>
+        <v/>
+      </c>
+      <c r="E149" s="15">
+        <f>E148-D148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C150" s="14">
+        <f>IF(B148=0,NA(),C148/B148-1)</f>
+        <v/>
+      </c>
+      <c r="D150" s="14">
+        <f>IF(C148=0,NA(),D148/C148-1)</f>
+        <v/>
+      </c>
+      <c r="E150" s="14">
+        <f>IF(D148=0,NA(),E148/D148-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C151" s="15">
+        <f>(B148+C148)/2</f>
+        <v/>
+      </c>
+      <c r="D151" s="15">
+        <f>(C148+D148)/2</f>
+        <v/>
+      </c>
+      <c r="E151" s="15">
+        <f>(D148+E148)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C149" s="14">
-        <f>IF('Condensed Financials'!C34=0,NA(),C148/'Condensed Financials'!C34)</f>
-        <v/>
-      </c>
-      <c r="D149" s="14">
-        <f>IF('Condensed Financials'!D34=0,NA(),D148/'Condensed Financials'!D34)</f>
-        <v/>
-      </c>
-      <c r="E149" s="14">
-        <f>IF('Condensed Financials'!E34=0,NA(),E148/'Condensed Financials'!E34)</f>
+      <c r="C152" s="14">
+        <f>IF('Condensed Financials'!C34=0,NA(),C151/'Condensed Financials'!C34)</f>
+        <v/>
+      </c>
+      <c r="D152" s="14">
+        <f>IF('Condensed Financials'!D34=0,NA(),D151/'Condensed Financials'!D34)</f>
+        <v/>
+      </c>
+      <c r="E152" s="14">
+        <f>IF('Condensed Financials'!E34=0,NA(),E151/'Condensed Financials'!E34)</f>
         <v/>
       </c>
     </row>
